--- a/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_uz_asesoramiento.xlsx
+++ b/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_uz_asesoramiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P652"/>
+  <dimension ref="A1:R652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +495,16 @@
       <c r="P1" t="inlineStr">
         <is>
           <t>ubigeo</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ugel</t>
         </is>
       </c>
     </row>
@@ -551,6 +561,8 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -605,6 +617,8 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -659,6 +673,8 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -713,6 +729,8 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -767,6 +785,8 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -821,6 +841,8 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -875,6 +897,8 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -929,6 +953,8 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -983,6 +1009,8 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1037,6 +1065,8 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1091,6 +1121,8 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1145,6 +1177,8 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1199,6 +1233,8 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1253,6 +1289,8 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1307,6 +1345,8 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1361,6 +1401,8 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1411,6 +1453,8 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1465,6 +1509,8 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1511,6 +1557,8 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1565,6 +1613,8 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1619,6 +1669,8 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1673,6 +1725,8 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1727,6 +1781,8 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1781,6 +1837,8 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1835,6 +1893,8 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1889,6 +1949,8 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1943,6 +2005,8 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1997,6 +2061,8 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2051,6 +2117,8 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2105,6 +2173,8 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2159,6 +2229,8 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2213,6 +2285,8 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2267,6 +2341,8 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2321,6 +2397,8 @@
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2375,6 +2453,8 @@
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2429,6 +2509,8 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2483,6 +2565,8 @@
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2535,6 +2619,8 @@
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2589,6 +2675,8 @@
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2643,6 +2731,8 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2697,6 +2787,8 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2751,6 +2843,8 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2805,6 +2899,8 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2859,6 +2955,8 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2913,6 +3011,8 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2967,6 +3067,8 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3021,6 +3123,8 @@
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3075,6 +3179,8 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3129,6 +3235,8 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3183,6 +3291,8 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3233,6 +3343,8 @@
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3287,6 +3399,8 @@
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3341,6 +3455,8 @@
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3395,6 +3511,8 @@
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3449,6 +3567,8 @@
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3503,6 +3623,8 @@
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3557,6 +3679,8 @@
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3611,6 +3735,8 @@
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3665,6 +3791,8 @@
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3719,6 +3847,8 @@
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3773,6 +3903,8 @@
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3825,6 +3957,8 @@
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3879,6 +4013,8 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3933,6 +4069,8 @@
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3987,6 +4125,8 @@
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4041,6 +4181,8 @@
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4095,6 +4237,8 @@
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4149,6 +4293,8 @@
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4203,6 +4349,8 @@
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4255,6 +4403,8 @@
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4307,6 +4457,8 @@
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4359,6 +4511,8 @@
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4411,6 +4565,8 @@
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4463,6 +4619,8 @@
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4515,6 +4673,8 @@
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4563,6 +4723,8 @@
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4611,6 +4773,8 @@
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4659,6 +4823,8 @@
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4707,6 +4873,8 @@
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4759,6 +4927,8 @@
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4811,6 +4981,8 @@
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4863,6 +5035,8 @@
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4915,6 +5089,8 @@
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4967,6 +5143,8 @@
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5015,6 +5193,8 @@
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5059,6 +5239,8 @@
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5111,6 +5293,8 @@
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5163,6 +5347,8 @@
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5215,6 +5401,8 @@
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5267,6 +5455,8 @@
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5319,6 +5509,8 @@
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5367,6 +5559,8 @@
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5421,6 +5615,8 @@
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5471,6 +5667,8 @@
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5521,6 +5719,8 @@
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5575,6 +5775,8 @@
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5629,6 +5831,8 @@
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5683,6 +5887,8 @@
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5737,6 +5943,8 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5791,6 +5999,8 @@
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5841,6 +6051,8 @@
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5891,6 +6103,8 @@
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5941,6 +6155,8 @@
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5987,6 +6203,8 @@
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6039,6 +6257,8 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6091,6 +6311,8 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6143,6 +6365,8 @@
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6195,6 +6419,8 @@
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6247,6 +6473,8 @@
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6299,6 +6527,8 @@
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6351,6 +6581,8 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6403,6 +6635,8 @@
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6451,6 +6685,8 @@
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6499,6 +6735,8 @@
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6547,6 +6785,8 @@
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6599,6 +6839,8 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6651,6 +6893,8 @@
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6703,6 +6947,8 @@
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -6755,6 +7001,8 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -6799,6 +7047,8 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -6843,6 +7093,8 @@
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -6887,6 +7139,8 @@
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6931,6 +7185,8 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6971,6 +7227,8 @@
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7011,6 +7269,8 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7055,6 +7315,8 @@
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7099,6 +7361,8 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7143,6 +7407,8 @@
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7187,6 +7453,8 @@
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7231,6 +7499,8 @@
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7285,6 +7555,8 @@
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7339,6 +7611,8 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7393,6 +7667,8 @@
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7447,6 +7723,8 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7501,6 +7779,8 @@
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7553,6 +7833,8 @@
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7607,6 +7889,8 @@
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -7661,6 +7945,8 @@
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -7715,6 +8001,8 @@
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7769,6 +8057,8 @@
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -7823,6 +8113,8 @@
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -7877,6 +8169,8 @@
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -7927,6 +8221,8 @@
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -7981,6 +8277,8 @@
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8031,6 +8329,8 @@
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8085,6 +8385,8 @@
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8135,6 +8437,8 @@
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8189,6 +8493,8 @@
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8243,6 +8549,8 @@
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8297,6 +8605,8 @@
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8351,6 +8661,8 @@
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8405,6 +8717,8 @@
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8459,6 +8773,8 @@
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8513,6 +8829,8 @@
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8567,6 +8885,8 @@
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8621,6 +8941,8 @@
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8675,6 +8997,8 @@
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -8725,6 +9049,8 @@
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -8775,6 +9101,8 @@
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8825,6 +9153,8 @@
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8875,6 +9205,8 @@
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8925,6 +9257,8 @@
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8975,6 +9309,8 @@
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9025,6 +9361,8 @@
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9075,6 +9413,8 @@
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9125,6 +9465,8 @@
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9175,6 +9517,8 @@
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -9225,6 +9569,8 @@
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -9275,6 +9621,8 @@
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9325,6 +9673,8 @@
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -9375,6 +9725,8 @@
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9425,6 +9777,8 @@
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -9475,6 +9829,8 @@
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -9525,6 +9881,8 @@
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9575,6 +9933,8 @@
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9625,6 +9985,8 @@
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -9675,6 +10037,8 @@
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -9725,6 +10089,8 @@
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -9775,6 +10141,8 @@
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9825,6 +10193,8 @@
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -9875,6 +10245,8 @@
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -9925,6 +10297,8 @@
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9975,6 +10349,8 @@
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10025,6 +10401,8 @@
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -10075,6 +10453,8 @@
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -10125,6 +10505,8 @@
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -10175,6 +10557,8 @@
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -10225,6 +10609,8 @@
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -10275,6 +10661,8 @@
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -10325,6 +10713,8 @@
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -10375,6 +10765,8 @@
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -10423,6 +10815,8 @@
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -10471,6 +10865,8 @@
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -10519,6 +10915,8 @@
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -10567,6 +10965,8 @@
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -10615,6 +11015,8 @@
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -10663,6 +11065,8 @@
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -10711,6 +11115,8 @@
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -10759,6 +11165,8 @@
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -10807,6 +11215,8 @@
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -10855,6 +11265,8 @@
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -10903,6 +11315,8 @@
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -10951,6 +11365,8 @@
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -11001,6 +11417,8 @@
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -11051,6 +11469,8 @@
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -11101,6 +11521,8 @@
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -11151,6 +11573,8 @@
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -11201,6 +11625,8 @@
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -11251,6 +11677,8 @@
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -11301,6 +11729,8 @@
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -11351,6 +11781,8 @@
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -11401,6 +11833,8 @@
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -11451,6 +11885,8 @@
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -11501,6 +11937,8 @@
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -11551,6 +11989,8 @@
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -11601,6 +12041,8 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -11649,6 +12091,8 @@
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -11697,6 +12141,8 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -11745,6 +12191,8 @@
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -11795,6 +12243,8 @@
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -11845,6 +12295,8 @@
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -11893,6 +12345,8 @@
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -11941,6 +12395,8 @@
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -11989,6 +12445,8 @@
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -12035,6 +12493,8 @@
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -12085,6 +12545,8 @@
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -12135,6 +12597,8 @@
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -12185,6 +12649,8 @@
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -12233,6 +12699,8 @@
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -12281,6 +12749,8 @@
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -12329,6 +12799,8 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -12377,6 +12849,8 @@
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -12427,6 +12901,8 @@
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -12477,6 +12953,8 @@
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -12525,6 +13003,8 @@
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -12573,6 +13053,8 @@
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -12623,6 +13105,8 @@
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -12673,6 +13157,8 @@
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -12723,6 +13209,8 @@
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -12773,6 +13261,8 @@
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -12823,6 +13313,8 @@
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -12873,6 +13365,8 @@
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -12921,6 +13415,8 @@
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -12971,6 +13467,8 @@
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -13019,6 +13517,8 @@
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -13069,6 +13569,8 @@
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -13117,6 +13619,8 @@
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -13167,6 +13671,8 @@
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -13215,6 +13721,8 @@
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
       <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -13265,6 +13773,8 @@
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
       <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -13313,6 +13823,8 @@
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -13359,6 +13871,8 @@
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -13409,6 +13923,8 @@
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -13459,6 +13975,8 @@
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -13509,6 +14027,8 @@
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -13559,6 +14079,8 @@
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -13609,6 +14131,8 @@
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -13659,6 +14183,8 @@
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -13709,6 +14235,8 @@
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -13759,6 +14287,8 @@
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -13809,6 +14339,8 @@
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -13859,6 +14391,8 @@
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -13909,6 +14443,8 @@
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -13959,6 +14495,8 @@
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -14009,6 +14547,8 @@
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -14059,6 +14599,8 @@
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -14109,6 +14651,8 @@
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -14159,6 +14703,8 @@
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr"/>
       <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -14209,6 +14755,8 @@
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -14259,6 +14807,8 @@
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -14309,6 +14859,8 @@
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -14359,6 +14911,8 @@
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -14409,6 +14963,8 @@
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -14459,6 +15015,8 @@
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
+      <c r="R275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -14509,6 +15067,8 @@
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
+      <c r="R276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -14559,6 +15119,8 @@
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
+      <c r="R277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -14609,6 +15171,8 @@
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
       <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="inlineStr"/>
+      <c r="R278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -14659,6 +15223,8 @@
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -14709,6 +15275,8 @@
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
       <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -14759,6 +15327,8 @@
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr"/>
       <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -14809,6 +15379,8 @@
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr"/>
       <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -14859,6 +15431,8 @@
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr"/>
       <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
+      <c r="R283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -14909,6 +15483,8 @@
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="inlineStr"/>
       <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
+      <c r="R284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -14959,6 +15535,8 @@
       <c r="N285" t="inlineStr"/>
       <c r="O285" t="inlineStr"/>
       <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
+      <c r="R285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -15009,6 +15587,8 @@
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
+      <c r="R286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -15059,6 +15639,8 @@
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -15109,6 +15691,8 @@
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
+      <c r="R288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -15159,6 +15743,8 @@
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
       <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
+      <c r="R289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -15209,6 +15795,8 @@
       <c r="N290" t="inlineStr"/>
       <c r="O290" t="inlineStr"/>
       <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
+      <c r="R290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -15259,6 +15847,8 @@
       <c r="N291" t="inlineStr"/>
       <c r="O291" t="inlineStr"/>
       <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
+      <c r="R291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -15309,6 +15899,8 @@
       <c r="N292" t="inlineStr"/>
       <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
+      <c r="R292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -15359,6 +15951,8 @@
       <c r="N293" t="inlineStr"/>
       <c r="O293" t="inlineStr"/>
       <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
+      <c r="R293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -15409,6 +16003,8 @@
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
+      <c r="R294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -15459,6 +16055,8 @@
       <c r="N295" t="inlineStr"/>
       <c r="O295" t="inlineStr"/>
       <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
+      <c r="R295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -15509,6 +16107,8 @@
       <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
+      <c r="R296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -15559,6 +16159,8 @@
       <c r="N297" t="inlineStr"/>
       <c r="O297" t="inlineStr"/>
       <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
+      <c r="R297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -15609,6 +16211,8 @@
       <c r="N298" t="inlineStr"/>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
+      <c r="R298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -15659,6 +16263,8 @@
       <c r="N299" t="inlineStr"/>
       <c r="O299" t="inlineStr"/>
       <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr"/>
+      <c r="R299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -15709,6 +16315,8 @@
       <c r="N300" t="inlineStr"/>
       <c r="O300" t="inlineStr"/>
       <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
+      <c r="R300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -15759,6 +16367,8 @@
       <c r="N301" t="inlineStr"/>
       <c r="O301" t="inlineStr"/>
       <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="inlineStr"/>
+      <c r="R301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -15809,6 +16419,8 @@
       <c r="N302" t="inlineStr"/>
       <c r="O302" t="inlineStr"/>
       <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="inlineStr"/>
+      <c r="R302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -15859,6 +16471,8 @@
       <c r="N303" t="inlineStr"/>
       <c r="O303" t="inlineStr"/>
       <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
+      <c r="R303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -15909,6 +16523,8 @@
       <c r="N304" t="inlineStr"/>
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="inlineStr"/>
+      <c r="R304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -15959,6 +16575,8 @@
       <c r="N305" t="inlineStr"/>
       <c r="O305" t="inlineStr"/>
       <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
+      <c r="R305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -16009,6 +16627,8 @@
       <c r="N306" t="inlineStr"/>
       <c r="O306" t="inlineStr"/>
       <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
+      <c r="R306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -16059,6 +16679,8 @@
       <c r="N307" t="inlineStr"/>
       <c r="O307" t="inlineStr"/>
       <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="inlineStr"/>
+      <c r="R307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -16109,6 +16731,8 @@
       <c r="N308" t="inlineStr"/>
       <c r="O308" t="inlineStr"/>
       <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
+      <c r="R308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -16159,6 +16783,8 @@
       <c r="N309" t="inlineStr"/>
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="inlineStr"/>
+      <c r="R309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -16209,6 +16835,8 @@
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
+      <c r="R310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -16259,6 +16887,8 @@
       <c r="N311" t="inlineStr"/>
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr"/>
+      <c r="R311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -16309,6 +16939,8 @@
       <c r="N312" t="inlineStr"/>
       <c r="O312" t="inlineStr"/>
       <c r="P312" t="inlineStr"/>
+      <c r="Q312" t="inlineStr"/>
+      <c r="R312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -16359,6 +16991,8 @@
       <c r="N313" t="inlineStr"/>
       <c r="O313" t="inlineStr"/>
       <c r="P313" t="inlineStr"/>
+      <c r="Q313" t="inlineStr"/>
+      <c r="R313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -16409,6 +17043,8 @@
       <c r="N314" t="inlineStr"/>
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="inlineStr"/>
+      <c r="Q314" t="inlineStr"/>
+      <c r="R314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -16459,6 +17095,8 @@
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr"/>
+      <c r="Q315" t="inlineStr"/>
+      <c r="R315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -16509,6 +17147,8 @@
       <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="inlineStr"/>
+      <c r="Q316" t="inlineStr"/>
+      <c r="R316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -16559,6 +17199,8 @@
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr"/>
       <c r="P317" t="inlineStr"/>
+      <c r="Q317" t="inlineStr"/>
+      <c r="R317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -16609,6 +17251,8 @@
       <c r="N318" t="inlineStr"/>
       <c r="O318" t="inlineStr"/>
       <c r="P318" t="inlineStr"/>
+      <c r="Q318" t="inlineStr"/>
+      <c r="R318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -16659,6 +17303,8 @@
       <c r="N319" t="inlineStr"/>
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="inlineStr"/>
+      <c r="R319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -16709,6 +17355,8 @@
       <c r="N320" t="inlineStr"/>
       <c r="O320" t="inlineStr"/>
       <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="inlineStr"/>
+      <c r="R320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -16759,6 +17407,8 @@
       <c r="N321" t="inlineStr"/>
       <c r="O321" t="inlineStr"/>
       <c r="P321" t="inlineStr"/>
+      <c r="Q321" t="inlineStr"/>
+      <c r="R321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -16809,6 +17459,8 @@
       <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="inlineStr"/>
+      <c r="Q322" t="inlineStr"/>
+      <c r="R322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -16859,6 +17511,8 @@
       <c r="N323" t="inlineStr"/>
       <c r="O323" t="inlineStr"/>
       <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
+      <c r="R323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -16909,6 +17563,8 @@
       <c r="N324" t="inlineStr"/>
       <c r="O324" t="inlineStr"/>
       <c r="P324" t="inlineStr"/>
+      <c r="Q324" t="inlineStr"/>
+      <c r="R324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -16959,6 +17615,8 @@
       <c r="N325" t="inlineStr"/>
       <c r="O325" t="inlineStr"/>
       <c r="P325" t="inlineStr"/>
+      <c r="Q325" t="inlineStr"/>
+      <c r="R325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -17009,6 +17667,8 @@
       <c r="N326" t="inlineStr"/>
       <c r="O326" t="inlineStr"/>
       <c r="P326" t="inlineStr"/>
+      <c r="Q326" t="inlineStr"/>
+      <c r="R326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -17059,6 +17719,8 @@
       <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr"/>
       <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
+      <c r="R327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -17109,6 +17771,8 @@
       <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr"/>
+      <c r="R328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -17159,6 +17823,8 @@
       <c r="N329" t="inlineStr"/>
       <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr"/>
+      <c r="Q329" t="inlineStr"/>
+      <c r="R329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -17209,6 +17875,8 @@
       <c r="N330" t="inlineStr"/>
       <c r="O330" t="inlineStr"/>
       <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="inlineStr"/>
+      <c r="R330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -17259,6 +17927,8 @@
       <c r="N331" t="inlineStr"/>
       <c r="O331" t="inlineStr"/>
       <c r="P331" t="inlineStr"/>
+      <c r="Q331" t="inlineStr"/>
+      <c r="R331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -17309,6 +17979,8 @@
       <c r="N332" t="inlineStr"/>
       <c r="O332" t="inlineStr"/>
       <c r="P332" t="inlineStr"/>
+      <c r="Q332" t="inlineStr"/>
+      <c r="R332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -17359,6 +18031,8 @@
       <c r="N333" t="inlineStr"/>
       <c r="O333" t="inlineStr"/>
       <c r="P333" t="inlineStr"/>
+      <c r="Q333" t="inlineStr"/>
+      <c r="R333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -17409,6 +18083,8 @@
       <c r="N334" t="inlineStr"/>
       <c r="O334" t="inlineStr"/>
       <c r="P334" t="inlineStr"/>
+      <c r="Q334" t="inlineStr"/>
+      <c r="R334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -17459,6 +18135,8 @@
       <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr"/>
       <c r="P335" t="inlineStr"/>
+      <c r="Q335" t="inlineStr"/>
+      <c r="R335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -17509,6 +18187,8 @@
       <c r="N336" t="inlineStr"/>
       <c r="O336" t="inlineStr"/>
       <c r="P336" t="inlineStr"/>
+      <c r="Q336" t="inlineStr"/>
+      <c r="R336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -17559,6 +18239,8 @@
       <c r="N337" t="inlineStr"/>
       <c r="O337" t="inlineStr"/>
       <c r="P337" t="inlineStr"/>
+      <c r="Q337" t="inlineStr"/>
+      <c r="R337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -17609,6 +18291,8 @@
       <c r="N338" t="inlineStr"/>
       <c r="O338" t="inlineStr"/>
       <c r="P338" t="inlineStr"/>
+      <c r="Q338" t="inlineStr"/>
+      <c r="R338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -17659,6 +18343,8 @@
       <c r="N339" t="inlineStr"/>
       <c r="O339" t="inlineStr"/>
       <c r="P339" t="inlineStr"/>
+      <c r="Q339" t="inlineStr"/>
+      <c r="R339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -17709,6 +18395,8 @@
       <c r="N340" t="inlineStr"/>
       <c r="O340" t="inlineStr"/>
       <c r="P340" t="inlineStr"/>
+      <c r="Q340" t="inlineStr"/>
+      <c r="R340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -17759,6 +18447,8 @@
       <c r="N341" t="inlineStr"/>
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="inlineStr"/>
+      <c r="Q341" t="inlineStr"/>
+      <c r="R341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -17809,6 +18499,8 @@
       <c r="N342" t="inlineStr"/>
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr"/>
+      <c r="Q342" t="inlineStr"/>
+      <c r="R342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -17859,6 +18551,8 @@
       <c r="N343" t="inlineStr"/>
       <c r="O343" t="inlineStr"/>
       <c r="P343" t="inlineStr"/>
+      <c r="Q343" t="inlineStr"/>
+      <c r="R343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -17909,6 +18603,8 @@
       <c r="N344" t="inlineStr"/>
       <c r="O344" t="inlineStr"/>
       <c r="P344" t="inlineStr"/>
+      <c r="Q344" t="inlineStr"/>
+      <c r="R344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -17959,6 +18655,8 @@
       <c r="N345" t="inlineStr"/>
       <c r="O345" t="inlineStr"/>
       <c r="P345" t="inlineStr"/>
+      <c r="Q345" t="inlineStr"/>
+      <c r="R345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -18009,6 +18707,8 @@
       <c r="N346" t="inlineStr"/>
       <c r="O346" t="inlineStr"/>
       <c r="P346" t="inlineStr"/>
+      <c r="Q346" t="inlineStr"/>
+      <c r="R346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -18059,6 +18759,8 @@
       <c r="N347" t="inlineStr"/>
       <c r="O347" t="inlineStr"/>
       <c r="P347" t="inlineStr"/>
+      <c r="Q347" t="inlineStr"/>
+      <c r="R347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -18109,6 +18811,8 @@
       <c r="N348" t="inlineStr"/>
       <c r="O348" t="inlineStr"/>
       <c r="P348" t="inlineStr"/>
+      <c r="Q348" t="inlineStr"/>
+      <c r="R348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -18159,6 +18863,8 @@
       <c r="N349" t="inlineStr"/>
       <c r="O349" t="inlineStr"/>
       <c r="P349" t="inlineStr"/>
+      <c r="Q349" t="inlineStr"/>
+      <c r="R349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -18209,6 +18915,8 @@
       <c r="N350" t="inlineStr"/>
       <c r="O350" t="inlineStr"/>
       <c r="P350" t="inlineStr"/>
+      <c r="Q350" t="inlineStr"/>
+      <c r="R350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -18259,6 +18967,8 @@
       <c r="N351" t="inlineStr"/>
       <c r="O351" t="inlineStr"/>
       <c r="P351" t="inlineStr"/>
+      <c r="Q351" t="inlineStr"/>
+      <c r="R351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -18309,6 +19019,8 @@
       <c r="N352" t="inlineStr"/>
       <c r="O352" t="inlineStr"/>
       <c r="P352" t="inlineStr"/>
+      <c r="Q352" t="inlineStr"/>
+      <c r="R352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -18359,6 +19071,8 @@
       <c r="N353" t="inlineStr"/>
       <c r="O353" t="inlineStr"/>
       <c r="P353" t="inlineStr"/>
+      <c r="Q353" t="inlineStr"/>
+      <c r="R353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -18409,6 +19123,8 @@
       <c r="N354" t="inlineStr"/>
       <c r="O354" t="inlineStr"/>
       <c r="P354" t="inlineStr"/>
+      <c r="Q354" t="inlineStr"/>
+      <c r="R354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -18459,6 +19175,8 @@
       <c r="N355" t="inlineStr"/>
       <c r="O355" t="inlineStr"/>
       <c r="P355" t="inlineStr"/>
+      <c r="Q355" t="inlineStr"/>
+      <c r="R355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -18509,6 +19227,8 @@
       <c r="N356" t="inlineStr"/>
       <c r="O356" t="inlineStr"/>
       <c r="P356" t="inlineStr"/>
+      <c r="Q356" t="inlineStr"/>
+      <c r="R356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -18559,6 +19279,8 @@
       <c r="N357" t="inlineStr"/>
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="inlineStr"/>
+      <c r="Q357" t="inlineStr"/>
+      <c r="R357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -18609,6 +19331,8 @@
       <c r="N358" t="inlineStr"/>
       <c r="O358" t="inlineStr"/>
       <c r="P358" t="inlineStr"/>
+      <c r="Q358" t="inlineStr"/>
+      <c r="R358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -18659,6 +19383,8 @@
       <c r="N359" t="inlineStr"/>
       <c r="O359" t="inlineStr"/>
       <c r="P359" t="inlineStr"/>
+      <c r="Q359" t="inlineStr"/>
+      <c r="R359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -18709,6 +19435,8 @@
       <c r="N360" t="inlineStr"/>
       <c r="O360" t="inlineStr"/>
       <c r="P360" t="inlineStr"/>
+      <c r="Q360" t="inlineStr"/>
+      <c r="R360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -18759,6 +19487,8 @@
       <c r="N361" t="inlineStr"/>
       <c r="O361" t="inlineStr"/>
       <c r="P361" t="inlineStr"/>
+      <c r="Q361" t="inlineStr"/>
+      <c r="R361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -18809,6 +19539,8 @@
       <c r="N362" t="inlineStr"/>
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="inlineStr"/>
+      <c r="Q362" t="inlineStr"/>
+      <c r="R362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -18859,6 +19591,8 @@
       <c r="N363" t="inlineStr"/>
       <c r="O363" t="inlineStr"/>
       <c r="P363" t="inlineStr"/>
+      <c r="Q363" t="inlineStr"/>
+      <c r="R363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -18909,6 +19643,8 @@
       <c r="N364" t="inlineStr"/>
       <c r="O364" t="inlineStr"/>
       <c r="P364" t="inlineStr"/>
+      <c r="Q364" t="inlineStr"/>
+      <c r="R364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -18959,6 +19695,8 @@
       <c r="N365" t="inlineStr"/>
       <c r="O365" t="inlineStr"/>
       <c r="P365" t="inlineStr"/>
+      <c r="Q365" t="inlineStr"/>
+      <c r="R365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -19009,6 +19747,8 @@
       <c r="N366" t="inlineStr"/>
       <c r="O366" t="inlineStr"/>
       <c r="P366" t="inlineStr"/>
+      <c r="Q366" t="inlineStr"/>
+      <c r="R366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -19059,6 +19799,8 @@
       <c r="N367" t="inlineStr"/>
       <c r="O367" t="inlineStr"/>
       <c r="P367" t="inlineStr"/>
+      <c r="Q367" t="inlineStr"/>
+      <c r="R367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -19109,6 +19851,8 @@
       <c r="N368" t="inlineStr"/>
       <c r="O368" t="inlineStr"/>
       <c r="P368" t="inlineStr"/>
+      <c r="Q368" t="inlineStr"/>
+      <c r="R368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -19159,6 +19903,8 @@
       <c r="N369" t="inlineStr"/>
       <c r="O369" t="inlineStr"/>
       <c r="P369" t="inlineStr"/>
+      <c r="Q369" t="inlineStr"/>
+      <c r="R369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -19209,6 +19955,8 @@
       <c r="N370" t="inlineStr"/>
       <c r="O370" t="inlineStr"/>
       <c r="P370" t="inlineStr"/>
+      <c r="Q370" t="inlineStr"/>
+      <c r="R370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -19259,6 +20007,8 @@
       <c r="N371" t="inlineStr"/>
       <c r="O371" t="inlineStr"/>
       <c r="P371" t="inlineStr"/>
+      <c r="Q371" t="inlineStr"/>
+      <c r="R371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -19309,6 +20059,8 @@
       <c r="N372" t="inlineStr"/>
       <c r="O372" t="inlineStr"/>
       <c r="P372" t="inlineStr"/>
+      <c r="Q372" t="inlineStr"/>
+      <c r="R372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -19359,6 +20111,8 @@
       <c r="N373" t="inlineStr"/>
       <c r="O373" t="inlineStr"/>
       <c r="P373" t="inlineStr"/>
+      <c r="Q373" t="inlineStr"/>
+      <c r="R373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -19409,6 +20163,8 @@
       <c r="N374" t="inlineStr"/>
       <c r="O374" t="inlineStr"/>
       <c r="P374" t="inlineStr"/>
+      <c r="Q374" t="inlineStr"/>
+      <c r="R374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -19459,6 +20215,8 @@
       <c r="N375" t="inlineStr"/>
       <c r="O375" t="inlineStr"/>
       <c r="P375" t="inlineStr"/>
+      <c r="Q375" t="inlineStr"/>
+      <c r="R375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -19509,6 +20267,8 @@
       <c r="N376" t="inlineStr"/>
       <c r="O376" t="inlineStr"/>
       <c r="P376" t="inlineStr"/>
+      <c r="Q376" t="inlineStr"/>
+      <c r="R376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -19559,6 +20319,8 @@
       <c r="N377" t="inlineStr"/>
       <c r="O377" t="inlineStr"/>
       <c r="P377" t="inlineStr"/>
+      <c r="Q377" t="inlineStr"/>
+      <c r="R377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -19609,6 +20371,8 @@
       <c r="N378" t="inlineStr"/>
       <c r="O378" t="inlineStr"/>
       <c r="P378" t="inlineStr"/>
+      <c r="Q378" t="inlineStr"/>
+      <c r="R378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -19659,6 +20423,8 @@
       <c r="N379" t="inlineStr"/>
       <c r="O379" t="inlineStr"/>
       <c r="P379" t="inlineStr"/>
+      <c r="Q379" t="inlineStr"/>
+      <c r="R379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -19709,6 +20475,8 @@
       <c r="N380" t="inlineStr"/>
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="inlineStr"/>
+      <c r="Q380" t="inlineStr"/>
+      <c r="R380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -19759,6 +20527,8 @@
       <c r="N381" t="inlineStr"/>
       <c r="O381" t="inlineStr"/>
       <c r="P381" t="inlineStr"/>
+      <c r="Q381" t="inlineStr"/>
+      <c r="R381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -19809,6 +20579,8 @@
       <c r="N382" t="inlineStr"/>
       <c r="O382" t="inlineStr"/>
       <c r="P382" t="inlineStr"/>
+      <c r="Q382" t="inlineStr"/>
+      <c r="R382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -19859,6 +20631,8 @@
       <c r="N383" t="inlineStr"/>
       <c r="O383" t="inlineStr"/>
       <c r="P383" t="inlineStr"/>
+      <c r="Q383" t="inlineStr"/>
+      <c r="R383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -19909,6 +20683,8 @@
       <c r="N384" t="inlineStr"/>
       <c r="O384" t="inlineStr"/>
       <c r="P384" t="inlineStr"/>
+      <c r="Q384" t="inlineStr"/>
+      <c r="R384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -19959,6 +20735,8 @@
       <c r="N385" t="inlineStr"/>
       <c r="O385" t="inlineStr"/>
       <c r="P385" t="inlineStr"/>
+      <c r="Q385" t="inlineStr"/>
+      <c r="R385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -20009,6 +20787,8 @@
       <c r="N386" t="inlineStr"/>
       <c r="O386" t="inlineStr"/>
       <c r="P386" t="inlineStr"/>
+      <c r="Q386" t="inlineStr"/>
+      <c r="R386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -20059,6 +20839,8 @@
       <c r="N387" t="inlineStr"/>
       <c r="O387" t="inlineStr"/>
       <c r="P387" t="inlineStr"/>
+      <c r="Q387" t="inlineStr"/>
+      <c r="R387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -20109,6 +20891,8 @@
       <c r="N388" t="inlineStr"/>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="inlineStr"/>
+      <c r="Q388" t="inlineStr"/>
+      <c r="R388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -20159,6 +20943,8 @@
       <c r="N389" t="inlineStr"/>
       <c r="O389" t="inlineStr"/>
       <c r="P389" t="inlineStr"/>
+      <c r="Q389" t="inlineStr"/>
+      <c r="R389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -20209,6 +20995,8 @@
       <c r="N390" t="inlineStr"/>
       <c r="O390" t="inlineStr"/>
       <c r="P390" t="inlineStr"/>
+      <c r="Q390" t="inlineStr"/>
+      <c r="R390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -20259,6 +21047,8 @@
       <c r="N391" t="inlineStr"/>
       <c r="O391" t="inlineStr"/>
       <c r="P391" t="inlineStr"/>
+      <c r="Q391" t="inlineStr"/>
+      <c r="R391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -20309,6 +21099,8 @@
       <c r="N392" t="inlineStr"/>
       <c r="O392" t="inlineStr"/>
       <c r="P392" t="inlineStr"/>
+      <c r="Q392" t="inlineStr"/>
+      <c r="R392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -20359,6 +21151,8 @@
       <c r="N393" t="inlineStr"/>
       <c r="O393" t="inlineStr"/>
       <c r="P393" t="inlineStr"/>
+      <c r="Q393" t="inlineStr"/>
+      <c r="R393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -20409,6 +21203,8 @@
       <c r="N394" t="inlineStr"/>
       <c r="O394" t="inlineStr"/>
       <c r="P394" t="inlineStr"/>
+      <c r="Q394" t="inlineStr"/>
+      <c r="R394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -20459,6 +21255,8 @@
       <c r="N395" t="inlineStr"/>
       <c r="O395" t="inlineStr"/>
       <c r="P395" t="inlineStr"/>
+      <c r="Q395" t="inlineStr"/>
+      <c r="R395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -20509,6 +21307,8 @@
       <c r="N396" t="inlineStr"/>
       <c r="O396" t="inlineStr"/>
       <c r="P396" t="inlineStr"/>
+      <c r="Q396" t="inlineStr"/>
+      <c r="R396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -20559,6 +21359,8 @@
       <c r="N397" t="inlineStr"/>
       <c r="O397" t="inlineStr"/>
       <c r="P397" t="inlineStr"/>
+      <c r="Q397" t="inlineStr"/>
+      <c r="R397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -20609,6 +21411,8 @@
       <c r="N398" t="inlineStr"/>
       <c r="O398" t="inlineStr"/>
       <c r="P398" t="inlineStr"/>
+      <c r="Q398" t="inlineStr"/>
+      <c r="R398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -20659,6 +21463,8 @@
       <c r="N399" t="inlineStr"/>
       <c r="O399" t="inlineStr"/>
       <c r="P399" t="inlineStr"/>
+      <c r="Q399" t="inlineStr"/>
+      <c r="R399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -20709,6 +21515,8 @@
       <c r="N400" t="inlineStr"/>
       <c r="O400" t="inlineStr"/>
       <c r="P400" t="inlineStr"/>
+      <c r="Q400" t="inlineStr"/>
+      <c r="R400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -20759,6 +21567,8 @@
       <c r="N401" t="inlineStr"/>
       <c r="O401" t="inlineStr"/>
       <c r="P401" t="inlineStr"/>
+      <c r="Q401" t="inlineStr"/>
+      <c r="R401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -20809,6 +21619,8 @@
       <c r="N402" t="inlineStr"/>
       <c r="O402" t="inlineStr"/>
       <c r="P402" t="inlineStr"/>
+      <c r="Q402" t="inlineStr"/>
+      <c r="R402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -20859,6 +21671,8 @@
       <c r="N403" t="inlineStr"/>
       <c r="O403" t="inlineStr"/>
       <c r="P403" t="inlineStr"/>
+      <c r="Q403" t="inlineStr"/>
+      <c r="R403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -20909,6 +21723,8 @@
       <c r="N404" t="inlineStr"/>
       <c r="O404" t="inlineStr"/>
       <c r="P404" t="inlineStr"/>
+      <c r="Q404" t="inlineStr"/>
+      <c r="R404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -20959,6 +21775,8 @@
       <c r="N405" t="inlineStr"/>
       <c r="O405" t="inlineStr"/>
       <c r="P405" t="inlineStr"/>
+      <c r="Q405" t="inlineStr"/>
+      <c r="R405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -21009,6 +21827,8 @@
       <c r="N406" t="inlineStr"/>
       <c r="O406" t="inlineStr"/>
       <c r="P406" t="inlineStr"/>
+      <c r="Q406" t="inlineStr"/>
+      <c r="R406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -21059,6 +21879,8 @@
       <c r="N407" t="inlineStr"/>
       <c r="O407" t="inlineStr"/>
       <c r="P407" t="inlineStr"/>
+      <c r="Q407" t="inlineStr"/>
+      <c r="R407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -21109,6 +21931,8 @@
       <c r="N408" t="inlineStr"/>
       <c r="O408" t="inlineStr"/>
       <c r="P408" t="inlineStr"/>
+      <c r="Q408" t="inlineStr"/>
+      <c r="R408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -21159,6 +21983,8 @@
       <c r="N409" t="inlineStr"/>
       <c r="O409" t="inlineStr"/>
       <c r="P409" t="inlineStr"/>
+      <c r="Q409" t="inlineStr"/>
+      <c r="R409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -21209,6 +22035,8 @@
       <c r="N410" t="inlineStr"/>
       <c r="O410" t="inlineStr"/>
       <c r="P410" t="inlineStr"/>
+      <c r="Q410" t="inlineStr"/>
+      <c r="R410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -21259,6 +22087,8 @@
       <c r="N411" t="inlineStr"/>
       <c r="O411" t="inlineStr"/>
       <c r="P411" t="inlineStr"/>
+      <c r="Q411" t="inlineStr"/>
+      <c r="R411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -21309,6 +22139,8 @@
       <c r="N412" t="inlineStr"/>
       <c r="O412" t="inlineStr"/>
       <c r="P412" t="inlineStr"/>
+      <c r="Q412" t="inlineStr"/>
+      <c r="R412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -21359,6 +22191,8 @@
       <c r="N413" t="inlineStr"/>
       <c r="O413" t="inlineStr"/>
       <c r="P413" t="inlineStr"/>
+      <c r="Q413" t="inlineStr"/>
+      <c r="R413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -21409,6 +22243,8 @@
       <c r="N414" t="inlineStr"/>
       <c r="O414" t="inlineStr"/>
       <c r="P414" t="inlineStr"/>
+      <c r="Q414" t="inlineStr"/>
+      <c r="R414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -21459,6 +22295,8 @@
       <c r="N415" t="inlineStr"/>
       <c r="O415" t="inlineStr"/>
       <c r="P415" t="inlineStr"/>
+      <c r="Q415" t="inlineStr"/>
+      <c r="R415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -21509,6 +22347,8 @@
       <c r="N416" t="inlineStr"/>
       <c r="O416" t="inlineStr"/>
       <c r="P416" t="inlineStr"/>
+      <c r="Q416" t="inlineStr"/>
+      <c r="R416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -21559,6 +22399,8 @@
       <c r="N417" t="inlineStr"/>
       <c r="O417" t="inlineStr"/>
       <c r="P417" t="inlineStr"/>
+      <c r="Q417" t="inlineStr"/>
+      <c r="R417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -21609,6 +22451,8 @@
       <c r="N418" t="inlineStr"/>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="inlineStr"/>
+      <c r="Q418" t="inlineStr"/>
+      <c r="R418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -21659,6 +22503,8 @@
       <c r="N419" t="inlineStr"/>
       <c r="O419" t="inlineStr"/>
       <c r="P419" t="inlineStr"/>
+      <c r="Q419" t="inlineStr"/>
+      <c r="R419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -21709,6 +22555,8 @@
       <c r="N420" t="inlineStr"/>
       <c r="O420" t="inlineStr"/>
       <c r="P420" t="inlineStr"/>
+      <c r="Q420" t="inlineStr"/>
+      <c r="R420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -21759,6 +22607,8 @@
       <c r="N421" t="inlineStr"/>
       <c r="O421" t="inlineStr"/>
       <c r="P421" t="inlineStr"/>
+      <c r="Q421" t="inlineStr"/>
+      <c r="R421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -21809,6 +22659,8 @@
       <c r="N422" t="inlineStr"/>
       <c r="O422" t="inlineStr"/>
       <c r="P422" t="inlineStr"/>
+      <c r="Q422" t="inlineStr"/>
+      <c r="R422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -21859,6 +22711,8 @@
       <c r="N423" t="inlineStr"/>
       <c r="O423" t="inlineStr"/>
       <c r="P423" t="inlineStr"/>
+      <c r="Q423" t="inlineStr"/>
+      <c r="R423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -21909,6 +22763,8 @@
       <c r="N424" t="inlineStr"/>
       <c r="O424" t="inlineStr"/>
       <c r="P424" t="inlineStr"/>
+      <c r="Q424" t="inlineStr"/>
+      <c r="R424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -21959,6 +22815,8 @@
       <c r="N425" t="inlineStr"/>
       <c r="O425" t="inlineStr"/>
       <c r="P425" t="inlineStr"/>
+      <c r="Q425" t="inlineStr"/>
+      <c r="R425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -22009,6 +22867,8 @@
       <c r="N426" t="inlineStr"/>
       <c r="O426" t="inlineStr"/>
       <c r="P426" t="inlineStr"/>
+      <c r="Q426" t="inlineStr"/>
+      <c r="R426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -22059,6 +22919,8 @@
       <c r="N427" t="inlineStr"/>
       <c r="O427" t="inlineStr"/>
       <c r="P427" t="inlineStr"/>
+      <c r="Q427" t="inlineStr"/>
+      <c r="R427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -22109,6 +22971,8 @@
       <c r="N428" t="inlineStr"/>
       <c r="O428" t="inlineStr"/>
       <c r="P428" t="inlineStr"/>
+      <c r="Q428" t="inlineStr"/>
+      <c r="R428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -22159,6 +23023,8 @@
       <c r="N429" t="inlineStr"/>
       <c r="O429" t="inlineStr"/>
       <c r="P429" t="inlineStr"/>
+      <c r="Q429" t="inlineStr"/>
+      <c r="R429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -22209,6 +23075,8 @@
       <c r="N430" t="inlineStr"/>
       <c r="O430" t="inlineStr"/>
       <c r="P430" t="inlineStr"/>
+      <c r="Q430" t="inlineStr"/>
+      <c r="R430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -22259,6 +23127,8 @@
       <c r="N431" t="inlineStr"/>
       <c r="O431" t="inlineStr"/>
       <c r="P431" t="inlineStr"/>
+      <c r="Q431" t="inlineStr"/>
+      <c r="R431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -22309,6 +23179,8 @@
       <c r="N432" t="inlineStr"/>
       <c r="O432" t="inlineStr"/>
       <c r="P432" t="inlineStr"/>
+      <c r="Q432" t="inlineStr"/>
+      <c r="R432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -22359,6 +23231,8 @@
       <c r="N433" t="inlineStr"/>
       <c r="O433" t="inlineStr"/>
       <c r="P433" t="inlineStr"/>
+      <c r="Q433" t="inlineStr"/>
+      <c r="R433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -22409,6 +23283,8 @@
       <c r="N434" t="inlineStr"/>
       <c r="O434" t="inlineStr"/>
       <c r="P434" t="inlineStr"/>
+      <c r="Q434" t="inlineStr"/>
+      <c r="R434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -22459,6 +23335,8 @@
       <c r="N435" t="inlineStr"/>
       <c r="O435" t="inlineStr"/>
       <c r="P435" t="inlineStr"/>
+      <c r="Q435" t="inlineStr"/>
+      <c r="R435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -22509,6 +23387,8 @@
       <c r="N436" t="inlineStr"/>
       <c r="O436" t="inlineStr"/>
       <c r="P436" t="inlineStr"/>
+      <c r="Q436" t="inlineStr"/>
+      <c r="R436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -22559,6 +23439,8 @@
       <c r="N437" t="inlineStr"/>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
+      <c r="Q437" t="inlineStr"/>
+      <c r="R437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -22609,6 +23491,8 @@
       <c r="N438" t="inlineStr"/>
       <c r="O438" t="inlineStr"/>
       <c r="P438" t="inlineStr"/>
+      <c r="Q438" t="inlineStr"/>
+      <c r="R438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -22659,6 +23543,8 @@
       <c r="N439" t="inlineStr"/>
       <c r="O439" t="inlineStr"/>
       <c r="P439" t="inlineStr"/>
+      <c r="Q439" t="inlineStr"/>
+      <c r="R439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -22709,6 +23595,8 @@
       <c r="N440" t="inlineStr"/>
       <c r="O440" t="inlineStr"/>
       <c r="P440" t="inlineStr"/>
+      <c r="Q440" t="inlineStr"/>
+      <c r="R440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -22759,6 +23647,8 @@
       <c r="N441" t="inlineStr"/>
       <c r="O441" t="inlineStr"/>
       <c r="P441" t="inlineStr"/>
+      <c r="Q441" t="inlineStr"/>
+      <c r="R441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -22809,6 +23699,8 @@
       <c r="N442" t="inlineStr"/>
       <c r="O442" t="inlineStr"/>
       <c r="P442" t="inlineStr"/>
+      <c r="Q442" t="inlineStr"/>
+      <c r="R442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -22859,6 +23751,8 @@
       <c r="N443" t="inlineStr"/>
       <c r="O443" t="inlineStr"/>
       <c r="P443" t="inlineStr"/>
+      <c r="Q443" t="inlineStr"/>
+      <c r="R443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -22909,6 +23803,8 @@
       <c r="N444" t="inlineStr"/>
       <c r="O444" t="inlineStr"/>
       <c r="P444" t="inlineStr"/>
+      <c r="Q444" t="inlineStr"/>
+      <c r="R444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -22959,6 +23855,8 @@
       <c r="N445" t="inlineStr"/>
       <c r="O445" t="inlineStr"/>
       <c r="P445" t="inlineStr"/>
+      <c r="Q445" t="inlineStr"/>
+      <c r="R445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -23009,6 +23907,8 @@
       <c r="N446" t="inlineStr"/>
       <c r="O446" t="inlineStr"/>
       <c r="P446" t="inlineStr"/>
+      <c r="Q446" t="inlineStr"/>
+      <c r="R446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -23059,6 +23959,8 @@
       <c r="N447" t="inlineStr"/>
       <c r="O447" t="inlineStr"/>
       <c r="P447" t="inlineStr"/>
+      <c r="Q447" t="inlineStr"/>
+      <c r="R447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -23109,6 +24011,8 @@
       <c r="N448" t="inlineStr"/>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="inlineStr"/>
+      <c r="Q448" t="inlineStr"/>
+      <c r="R448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -23159,6 +24063,8 @@
       <c r="N449" t="inlineStr"/>
       <c r="O449" t="inlineStr"/>
       <c r="P449" t="inlineStr"/>
+      <c r="Q449" t="inlineStr"/>
+      <c r="R449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -23209,6 +24115,8 @@
       <c r="N450" t="inlineStr"/>
       <c r="O450" t="inlineStr"/>
       <c r="P450" t="inlineStr"/>
+      <c r="Q450" t="inlineStr"/>
+      <c r="R450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -23259,6 +24167,8 @@
       <c r="N451" t="inlineStr"/>
       <c r="O451" t="inlineStr"/>
       <c r="P451" t="inlineStr"/>
+      <c r="Q451" t="inlineStr"/>
+      <c r="R451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -23309,6 +24219,8 @@
       <c r="N452" t="inlineStr"/>
       <c r="O452" t="inlineStr"/>
       <c r="P452" t="inlineStr"/>
+      <c r="Q452" t="inlineStr"/>
+      <c r="R452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -23359,6 +24271,8 @@
       <c r="N453" t="inlineStr"/>
       <c r="O453" t="inlineStr"/>
       <c r="P453" t="inlineStr"/>
+      <c r="Q453" t="inlineStr"/>
+      <c r="R453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -23409,6 +24323,8 @@
       <c r="N454" t="inlineStr"/>
       <c r="O454" t="inlineStr"/>
       <c r="P454" t="inlineStr"/>
+      <c r="Q454" t="inlineStr"/>
+      <c r="R454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -23459,6 +24375,8 @@
       <c r="N455" t="inlineStr"/>
       <c r="O455" t="inlineStr"/>
       <c r="P455" t="inlineStr"/>
+      <c r="Q455" t="inlineStr"/>
+      <c r="R455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -23509,6 +24427,8 @@
       <c r="N456" t="inlineStr"/>
       <c r="O456" t="inlineStr"/>
       <c r="P456" t="inlineStr"/>
+      <c r="Q456" t="inlineStr"/>
+      <c r="R456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -23559,6 +24479,8 @@
       <c r="N457" t="inlineStr"/>
       <c r="O457" t="inlineStr"/>
       <c r="P457" t="inlineStr"/>
+      <c r="Q457" t="inlineStr"/>
+      <c r="R457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -23609,6 +24531,8 @@
       <c r="N458" t="inlineStr"/>
       <c r="O458" t="inlineStr"/>
       <c r="P458" t="inlineStr"/>
+      <c r="Q458" t="inlineStr"/>
+      <c r="R458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -23659,6 +24583,8 @@
       <c r="N459" t="inlineStr"/>
       <c r="O459" t="inlineStr"/>
       <c r="P459" t="inlineStr"/>
+      <c r="Q459" t="inlineStr"/>
+      <c r="R459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -23709,6 +24635,8 @@
       <c r="N460" t="inlineStr"/>
       <c r="O460" t="inlineStr"/>
       <c r="P460" t="inlineStr"/>
+      <c r="Q460" t="inlineStr"/>
+      <c r="R460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -23759,6 +24687,8 @@
       <c r="N461" t="inlineStr"/>
       <c r="O461" t="inlineStr"/>
       <c r="P461" t="inlineStr"/>
+      <c r="Q461" t="inlineStr"/>
+      <c r="R461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -23809,6 +24739,8 @@
       <c r="N462" t="inlineStr"/>
       <c r="O462" t="inlineStr"/>
       <c r="P462" t="inlineStr"/>
+      <c r="Q462" t="inlineStr"/>
+      <c r="R462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -23859,6 +24791,8 @@
       <c r="N463" t="inlineStr"/>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="inlineStr"/>
+      <c r="Q463" t="inlineStr"/>
+      <c r="R463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -23909,6 +24843,8 @@
       <c r="N464" t="inlineStr"/>
       <c r="O464" t="inlineStr"/>
       <c r="P464" t="inlineStr"/>
+      <c r="Q464" t="inlineStr"/>
+      <c r="R464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -23959,6 +24895,8 @@
       <c r="N465" t="inlineStr"/>
       <c r="O465" t="inlineStr"/>
       <c r="P465" t="inlineStr"/>
+      <c r="Q465" t="inlineStr"/>
+      <c r="R465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -24009,6 +24947,8 @@
       <c r="N466" t="inlineStr"/>
       <c r="O466" t="inlineStr"/>
       <c r="P466" t="inlineStr"/>
+      <c r="Q466" t="inlineStr"/>
+      <c r="R466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -24059,6 +24999,8 @@
       <c r="N467" t="inlineStr"/>
       <c r="O467" t="inlineStr"/>
       <c r="P467" t="inlineStr"/>
+      <c r="Q467" t="inlineStr"/>
+      <c r="R467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -24109,6 +25051,8 @@
       <c r="N468" t="inlineStr"/>
       <c r="O468" t="inlineStr"/>
       <c r="P468" t="inlineStr"/>
+      <c r="Q468" t="inlineStr"/>
+      <c r="R468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -24159,6 +25103,8 @@
       <c r="N469" t="inlineStr"/>
       <c r="O469" t="inlineStr"/>
       <c r="P469" t="inlineStr"/>
+      <c r="Q469" t="inlineStr"/>
+      <c r="R469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -24209,6 +25155,8 @@
       <c r="N470" t="inlineStr"/>
       <c r="O470" t="inlineStr"/>
       <c r="P470" t="inlineStr"/>
+      <c r="Q470" t="inlineStr"/>
+      <c r="R470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -24259,6 +25207,8 @@
       <c r="N471" t="inlineStr"/>
       <c r="O471" t="inlineStr"/>
       <c r="P471" t="inlineStr"/>
+      <c r="Q471" t="inlineStr"/>
+      <c r="R471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -24309,6 +25259,8 @@
       <c r="N472" t="inlineStr"/>
       <c r="O472" t="inlineStr"/>
       <c r="P472" t="inlineStr"/>
+      <c r="Q472" t="inlineStr"/>
+      <c r="R472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -24359,6 +25311,8 @@
       <c r="N473" t="inlineStr"/>
       <c r="O473" t="inlineStr"/>
       <c r="P473" t="inlineStr"/>
+      <c r="Q473" t="inlineStr"/>
+      <c r="R473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -24409,6 +25363,8 @@
       <c r="N474" t="inlineStr"/>
       <c r="O474" t="inlineStr"/>
       <c r="P474" t="inlineStr"/>
+      <c r="Q474" t="inlineStr"/>
+      <c r="R474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -24459,6 +25415,8 @@
       <c r="N475" t="inlineStr"/>
       <c r="O475" t="inlineStr"/>
       <c r="P475" t="inlineStr"/>
+      <c r="Q475" t="inlineStr"/>
+      <c r="R475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -24509,6 +25467,8 @@
       <c r="N476" t="inlineStr"/>
       <c r="O476" t="inlineStr"/>
       <c r="P476" t="inlineStr"/>
+      <c r="Q476" t="inlineStr"/>
+      <c r="R476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -24559,6 +25519,8 @@
       <c r="N477" t="inlineStr"/>
       <c r="O477" t="inlineStr"/>
       <c r="P477" t="inlineStr"/>
+      <c r="Q477" t="inlineStr"/>
+      <c r="R477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -24609,6 +25571,8 @@
       <c r="N478" t="inlineStr"/>
       <c r="O478" t="inlineStr"/>
       <c r="P478" t="inlineStr"/>
+      <c r="Q478" t="inlineStr"/>
+      <c r="R478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -24659,6 +25623,8 @@
       <c r="N479" t="inlineStr"/>
       <c r="O479" t="inlineStr"/>
       <c r="P479" t="inlineStr"/>
+      <c r="Q479" t="inlineStr"/>
+      <c r="R479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -24709,6 +25675,8 @@
       <c r="N480" t="inlineStr"/>
       <c r="O480" t="inlineStr"/>
       <c r="P480" t="inlineStr"/>
+      <c r="Q480" t="inlineStr"/>
+      <c r="R480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -24759,6 +25727,8 @@
       <c r="N481" t="inlineStr"/>
       <c r="O481" t="inlineStr"/>
       <c r="P481" t="inlineStr"/>
+      <c r="Q481" t="inlineStr"/>
+      <c r="R481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -24809,6 +25779,8 @@
       <c r="N482" t="inlineStr"/>
       <c r="O482" t="inlineStr"/>
       <c r="P482" t="inlineStr"/>
+      <c r="Q482" t="inlineStr"/>
+      <c r="R482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -24859,6 +25831,8 @@
       <c r="N483" t="inlineStr"/>
       <c r="O483" t="inlineStr"/>
       <c r="P483" t="inlineStr"/>
+      <c r="Q483" t="inlineStr"/>
+      <c r="R483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -24909,6 +25883,8 @@
       <c r="N484" t="inlineStr"/>
       <c r="O484" t="inlineStr"/>
       <c r="P484" t="inlineStr"/>
+      <c r="Q484" t="inlineStr"/>
+      <c r="R484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -24959,6 +25935,8 @@
       <c r="N485" t="inlineStr"/>
       <c r="O485" t="inlineStr"/>
       <c r="P485" t="inlineStr"/>
+      <c r="Q485" t="inlineStr"/>
+      <c r="R485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -25009,6 +25987,8 @@
       <c r="N486" t="inlineStr"/>
       <c r="O486" t="inlineStr"/>
       <c r="P486" t="inlineStr"/>
+      <c r="Q486" t="inlineStr"/>
+      <c r="R486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -25059,6 +26039,8 @@
       <c r="N487" t="inlineStr"/>
       <c r="O487" t="inlineStr"/>
       <c r="P487" t="inlineStr"/>
+      <c r="Q487" t="inlineStr"/>
+      <c r="R487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -25109,6 +26091,8 @@
       <c r="N488" t="inlineStr"/>
       <c r="O488" t="inlineStr"/>
       <c r="P488" t="inlineStr"/>
+      <c r="Q488" t="inlineStr"/>
+      <c r="R488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -25159,6 +26143,8 @@
       <c r="N489" t="inlineStr"/>
       <c r="O489" t="inlineStr"/>
       <c r="P489" t="inlineStr"/>
+      <c r="Q489" t="inlineStr"/>
+      <c r="R489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -25209,6 +26195,8 @@
       <c r="N490" t="inlineStr"/>
       <c r="O490" t="inlineStr"/>
       <c r="P490" t="inlineStr"/>
+      <c r="Q490" t="inlineStr"/>
+      <c r="R490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -25259,6 +26247,8 @@
       <c r="N491" t="inlineStr"/>
       <c r="O491" t="inlineStr"/>
       <c r="P491" t="inlineStr"/>
+      <c r="Q491" t="inlineStr"/>
+      <c r="R491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -25309,6 +26299,8 @@
       <c r="N492" t="inlineStr"/>
       <c r="O492" t="inlineStr"/>
       <c r="P492" t="inlineStr"/>
+      <c r="Q492" t="inlineStr"/>
+      <c r="R492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -25359,6 +26351,8 @@
       <c r="N493" t="inlineStr"/>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="inlineStr"/>
+      <c r="Q493" t="inlineStr"/>
+      <c r="R493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -25409,6 +26403,8 @@
       <c r="N494" t="inlineStr"/>
       <c r="O494" t="inlineStr"/>
       <c r="P494" t="inlineStr"/>
+      <c r="Q494" t="inlineStr"/>
+      <c r="R494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -25459,6 +26455,8 @@
       <c r="N495" t="inlineStr"/>
       <c r="O495" t="inlineStr"/>
       <c r="P495" t="inlineStr"/>
+      <c r="Q495" t="inlineStr"/>
+      <c r="R495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -25509,6 +26507,8 @@
       <c r="N496" t="inlineStr"/>
       <c r="O496" t="inlineStr"/>
       <c r="P496" t="inlineStr"/>
+      <c r="Q496" t="inlineStr"/>
+      <c r="R496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -25559,6 +26559,8 @@
       <c r="N497" t="inlineStr"/>
       <c r="O497" t="inlineStr"/>
       <c r="P497" t="inlineStr"/>
+      <c r="Q497" t="inlineStr"/>
+      <c r="R497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -25609,6 +26611,8 @@
       <c r="N498" t="inlineStr"/>
       <c r="O498" t="inlineStr"/>
       <c r="P498" t="inlineStr"/>
+      <c r="Q498" t="inlineStr"/>
+      <c r="R498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -25659,6 +26663,8 @@
       <c r="N499" t="inlineStr"/>
       <c r="O499" t="inlineStr"/>
       <c r="P499" t="inlineStr"/>
+      <c r="Q499" t="inlineStr"/>
+      <c r="R499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -25709,6 +26715,8 @@
       <c r="N500" t="inlineStr"/>
       <c r="O500" t="inlineStr"/>
       <c r="P500" t="inlineStr"/>
+      <c r="Q500" t="inlineStr"/>
+      <c r="R500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -25759,6 +26767,8 @@
       <c r="N501" t="inlineStr"/>
       <c r="O501" t="inlineStr"/>
       <c r="P501" t="inlineStr"/>
+      <c r="Q501" t="inlineStr"/>
+      <c r="R501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -25809,6 +26819,8 @@
       <c r="N502" t="inlineStr"/>
       <c r="O502" t="inlineStr"/>
       <c r="P502" t="inlineStr"/>
+      <c r="Q502" t="inlineStr"/>
+      <c r="R502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -25859,6 +26871,8 @@
       <c r="N503" t="inlineStr"/>
       <c r="O503" t="inlineStr"/>
       <c r="P503" t="inlineStr"/>
+      <c r="Q503" t="inlineStr"/>
+      <c r="R503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -25909,6 +26923,8 @@
       <c r="N504" t="inlineStr"/>
       <c r="O504" t="inlineStr"/>
       <c r="P504" t="inlineStr"/>
+      <c r="Q504" t="inlineStr"/>
+      <c r="R504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -25959,6 +26975,8 @@
       <c r="N505" t="inlineStr"/>
       <c r="O505" t="inlineStr"/>
       <c r="P505" t="inlineStr"/>
+      <c r="Q505" t="inlineStr"/>
+      <c r="R505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -26009,6 +27027,8 @@
       <c r="N506" t="inlineStr"/>
       <c r="O506" t="inlineStr"/>
       <c r="P506" t="inlineStr"/>
+      <c r="Q506" t="inlineStr"/>
+      <c r="R506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -26059,6 +27079,8 @@
       <c r="N507" t="inlineStr"/>
       <c r="O507" t="inlineStr"/>
       <c r="P507" t="inlineStr"/>
+      <c r="Q507" t="inlineStr"/>
+      <c r="R507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -26109,6 +27131,8 @@
       <c r="N508" t="inlineStr"/>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="inlineStr"/>
+      <c r="Q508" t="inlineStr"/>
+      <c r="R508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -26159,6 +27183,8 @@
       <c r="N509" t="inlineStr"/>
       <c r="O509" t="inlineStr"/>
       <c r="P509" t="inlineStr"/>
+      <c r="Q509" t="inlineStr"/>
+      <c r="R509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -26209,6 +27235,8 @@
       <c r="N510" t="inlineStr"/>
       <c r="O510" t="inlineStr"/>
       <c r="P510" t="inlineStr"/>
+      <c r="Q510" t="inlineStr"/>
+      <c r="R510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -26259,6 +27287,8 @@
       <c r="N511" t="inlineStr"/>
       <c r="O511" t="inlineStr"/>
       <c r="P511" t="inlineStr"/>
+      <c r="Q511" t="inlineStr"/>
+      <c r="R511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -26309,6 +27339,8 @@
       <c r="N512" t="inlineStr"/>
       <c r="O512" t="inlineStr"/>
       <c r="P512" t="inlineStr"/>
+      <c r="Q512" t="inlineStr"/>
+      <c r="R512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -26359,6 +27391,8 @@
       <c r="N513" t="inlineStr"/>
       <c r="O513" t="inlineStr"/>
       <c r="P513" t="inlineStr"/>
+      <c r="Q513" t="inlineStr"/>
+      <c r="R513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -26409,6 +27443,8 @@
       <c r="N514" t="inlineStr"/>
       <c r="O514" t="inlineStr"/>
       <c r="P514" t="inlineStr"/>
+      <c r="Q514" t="inlineStr"/>
+      <c r="R514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -26459,6 +27495,8 @@
       <c r="N515" t="inlineStr"/>
       <c r="O515" t="inlineStr"/>
       <c r="P515" t="inlineStr"/>
+      <c r="Q515" t="inlineStr"/>
+      <c r="R515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -26509,6 +27547,8 @@
       <c r="N516" t="inlineStr"/>
       <c r="O516" t="inlineStr"/>
       <c r="P516" t="inlineStr"/>
+      <c r="Q516" t="inlineStr"/>
+      <c r="R516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -26559,6 +27599,8 @@
       <c r="N517" t="inlineStr"/>
       <c r="O517" t="inlineStr"/>
       <c r="P517" t="inlineStr"/>
+      <c r="Q517" t="inlineStr"/>
+      <c r="R517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -26609,6 +27651,8 @@
       <c r="N518" t="inlineStr"/>
       <c r="O518" t="inlineStr"/>
       <c r="P518" t="inlineStr"/>
+      <c r="Q518" t="inlineStr"/>
+      <c r="R518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -26659,6 +27703,8 @@
       <c r="N519" t="inlineStr"/>
       <c r="O519" t="inlineStr"/>
       <c r="P519" t="inlineStr"/>
+      <c r="Q519" t="inlineStr"/>
+      <c r="R519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -26709,6 +27755,8 @@
       <c r="N520" t="inlineStr"/>
       <c r="O520" t="inlineStr"/>
       <c r="P520" t="inlineStr"/>
+      <c r="Q520" t="inlineStr"/>
+      <c r="R520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -26759,6 +27807,8 @@
       <c r="N521" t="inlineStr"/>
       <c r="O521" t="inlineStr"/>
       <c r="P521" t="inlineStr"/>
+      <c r="Q521" t="inlineStr"/>
+      <c r="R521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -26809,6 +27859,8 @@
       <c r="N522" t="inlineStr"/>
       <c r="O522" t="inlineStr"/>
       <c r="P522" t="inlineStr"/>
+      <c r="Q522" t="inlineStr"/>
+      <c r="R522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -26859,6 +27911,8 @@
       <c r="N523" t="inlineStr"/>
       <c r="O523" t="inlineStr"/>
       <c r="P523" t="inlineStr"/>
+      <c r="Q523" t="inlineStr"/>
+      <c r="R523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -26909,6 +27963,8 @@
       <c r="N524" t="inlineStr"/>
       <c r="O524" t="inlineStr"/>
       <c r="P524" t="inlineStr"/>
+      <c r="Q524" t="inlineStr"/>
+      <c r="R524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -26959,6 +28015,8 @@
       <c r="N525" t="inlineStr"/>
       <c r="O525" t="inlineStr"/>
       <c r="P525" t="inlineStr"/>
+      <c r="Q525" t="inlineStr"/>
+      <c r="R525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -27009,6 +28067,8 @@
       <c r="N526" t="inlineStr"/>
       <c r="O526" t="inlineStr"/>
       <c r="P526" t="inlineStr"/>
+      <c r="Q526" t="inlineStr"/>
+      <c r="R526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -27059,6 +28119,8 @@
       <c r="N527" t="inlineStr"/>
       <c r="O527" t="inlineStr"/>
       <c r="P527" t="inlineStr"/>
+      <c r="Q527" t="inlineStr"/>
+      <c r="R527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -27109,6 +28171,8 @@
       <c r="N528" t="inlineStr"/>
       <c r="O528" t="inlineStr"/>
       <c r="P528" t="inlineStr"/>
+      <c r="Q528" t="inlineStr"/>
+      <c r="R528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -27159,6 +28223,8 @@
       <c r="N529" t="inlineStr"/>
       <c r="O529" t="inlineStr"/>
       <c r="P529" t="inlineStr"/>
+      <c r="Q529" t="inlineStr"/>
+      <c r="R529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -27209,6 +28275,8 @@
       <c r="N530" t="inlineStr"/>
       <c r="O530" t="inlineStr"/>
       <c r="P530" t="inlineStr"/>
+      <c r="Q530" t="inlineStr"/>
+      <c r="R530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -27259,6 +28327,8 @@
       <c r="N531" t="inlineStr"/>
       <c r="O531" t="inlineStr"/>
       <c r="P531" t="inlineStr"/>
+      <c r="Q531" t="inlineStr"/>
+      <c r="R531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -27309,6 +28379,8 @@
       <c r="N532" t="inlineStr"/>
       <c r="O532" t="inlineStr"/>
       <c r="P532" t="inlineStr"/>
+      <c r="Q532" t="inlineStr"/>
+      <c r="R532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -27359,6 +28431,8 @@
       <c r="N533" t="inlineStr"/>
       <c r="O533" t="inlineStr"/>
       <c r="P533" t="inlineStr"/>
+      <c r="Q533" t="inlineStr"/>
+      <c r="R533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -27409,6 +28483,8 @@
       <c r="N534" t="inlineStr"/>
       <c r="O534" t="inlineStr"/>
       <c r="P534" t="inlineStr"/>
+      <c r="Q534" t="inlineStr"/>
+      <c r="R534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -27459,6 +28535,8 @@
       <c r="N535" t="inlineStr"/>
       <c r="O535" t="inlineStr"/>
       <c r="P535" t="inlineStr"/>
+      <c r="Q535" t="inlineStr"/>
+      <c r="R535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -27509,6 +28587,8 @@
       <c r="N536" t="inlineStr"/>
       <c r="O536" t="inlineStr"/>
       <c r="P536" t="inlineStr"/>
+      <c r="Q536" t="inlineStr"/>
+      <c r="R536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -27559,6 +28639,8 @@
       <c r="N537" t="inlineStr"/>
       <c r="O537" t="inlineStr"/>
       <c r="P537" t="inlineStr"/>
+      <c r="Q537" t="inlineStr"/>
+      <c r="R537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -27609,6 +28691,8 @@
       <c r="N538" t="inlineStr"/>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="inlineStr"/>
+      <c r="Q538" t="inlineStr"/>
+      <c r="R538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -27659,6 +28743,8 @@
       <c r="N539" t="inlineStr"/>
       <c r="O539" t="inlineStr"/>
       <c r="P539" t="inlineStr"/>
+      <c r="Q539" t="inlineStr"/>
+      <c r="R539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -27709,6 +28795,8 @@
       <c r="N540" t="inlineStr"/>
       <c r="O540" t="inlineStr"/>
       <c r="P540" t="inlineStr"/>
+      <c r="Q540" t="inlineStr"/>
+      <c r="R540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -27759,6 +28847,8 @@
       <c r="N541" t="inlineStr"/>
       <c r="O541" t="inlineStr"/>
       <c r="P541" t="inlineStr"/>
+      <c r="Q541" t="inlineStr"/>
+      <c r="R541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -27809,6 +28899,8 @@
       <c r="N542" t="inlineStr"/>
       <c r="O542" t="inlineStr"/>
       <c r="P542" t="inlineStr"/>
+      <c r="Q542" t="inlineStr"/>
+      <c r="R542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -27859,6 +28951,8 @@
       <c r="N543" t="inlineStr"/>
       <c r="O543" t="inlineStr"/>
       <c r="P543" t="inlineStr"/>
+      <c r="Q543" t="inlineStr"/>
+      <c r="R543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -27909,6 +29003,8 @@
       <c r="N544" t="inlineStr"/>
       <c r="O544" t="inlineStr"/>
       <c r="P544" t="inlineStr"/>
+      <c r="Q544" t="inlineStr"/>
+      <c r="R544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -27959,6 +29055,8 @@
       <c r="N545" t="inlineStr"/>
       <c r="O545" t="inlineStr"/>
       <c r="P545" t="inlineStr"/>
+      <c r="Q545" t="inlineStr"/>
+      <c r="R545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -28009,6 +29107,8 @@
       <c r="N546" t="inlineStr"/>
       <c r="O546" t="inlineStr"/>
       <c r="P546" t="inlineStr"/>
+      <c r="Q546" t="inlineStr"/>
+      <c r="R546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -28059,6 +29159,8 @@
       <c r="N547" t="inlineStr"/>
       <c r="O547" t="inlineStr"/>
       <c r="P547" t="inlineStr"/>
+      <c r="Q547" t="inlineStr"/>
+      <c r="R547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -28109,6 +29211,8 @@
       <c r="N548" t="inlineStr"/>
       <c r="O548" t="inlineStr"/>
       <c r="P548" t="inlineStr"/>
+      <c r="Q548" t="inlineStr"/>
+      <c r="R548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -28159,6 +29263,8 @@
       <c r="N549" t="inlineStr"/>
       <c r="O549" t="inlineStr"/>
       <c r="P549" t="inlineStr"/>
+      <c r="Q549" t="inlineStr"/>
+      <c r="R549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -28209,6 +29315,8 @@
       <c r="N550" t="inlineStr"/>
       <c r="O550" t="inlineStr"/>
       <c r="P550" t="inlineStr"/>
+      <c r="Q550" t="inlineStr"/>
+      <c r="R550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -28259,6 +29367,8 @@
       <c r="N551" t="inlineStr"/>
       <c r="O551" t="inlineStr"/>
       <c r="P551" t="inlineStr"/>
+      <c r="Q551" t="inlineStr"/>
+      <c r="R551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -28309,6 +29419,8 @@
       <c r="N552" t="inlineStr"/>
       <c r="O552" t="inlineStr"/>
       <c r="P552" t="inlineStr"/>
+      <c r="Q552" t="inlineStr"/>
+      <c r="R552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -28359,6 +29471,8 @@
       <c r="N553" t="inlineStr"/>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="inlineStr"/>
+      <c r="Q553" t="inlineStr"/>
+      <c r="R553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -28409,6 +29523,8 @@
       <c r="N554" t="inlineStr"/>
       <c r="O554" t="inlineStr"/>
       <c r="P554" t="inlineStr"/>
+      <c r="Q554" t="inlineStr"/>
+      <c r="R554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -28459,6 +29575,8 @@
       <c r="N555" t="inlineStr"/>
       <c r="O555" t="inlineStr"/>
       <c r="P555" t="inlineStr"/>
+      <c r="Q555" t="inlineStr"/>
+      <c r="R555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -28509,6 +29627,8 @@
       <c r="N556" t="inlineStr"/>
       <c r="O556" t="inlineStr"/>
       <c r="P556" t="inlineStr"/>
+      <c r="Q556" t="inlineStr"/>
+      <c r="R556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -28559,6 +29679,8 @@
       <c r="N557" t="inlineStr"/>
       <c r="O557" t="inlineStr"/>
       <c r="P557" t="inlineStr"/>
+      <c r="Q557" t="inlineStr"/>
+      <c r="R557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -28609,6 +29731,8 @@
       <c r="N558" t="inlineStr"/>
       <c r="O558" t="inlineStr"/>
       <c r="P558" t="inlineStr"/>
+      <c r="Q558" t="inlineStr"/>
+      <c r="R558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -28659,6 +29783,8 @@
       <c r="N559" t="inlineStr"/>
       <c r="O559" t="inlineStr"/>
       <c r="P559" t="inlineStr"/>
+      <c r="Q559" t="inlineStr"/>
+      <c r="R559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -28709,6 +29835,8 @@
       <c r="N560" t="inlineStr"/>
       <c r="O560" t="inlineStr"/>
       <c r="P560" t="inlineStr"/>
+      <c r="Q560" t="inlineStr"/>
+      <c r="R560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -28759,6 +29887,8 @@
       <c r="N561" t="inlineStr"/>
       <c r="O561" t="inlineStr"/>
       <c r="P561" t="inlineStr"/>
+      <c r="Q561" t="inlineStr"/>
+      <c r="R561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -28809,6 +29939,8 @@
       <c r="N562" t="inlineStr"/>
       <c r="O562" t="inlineStr"/>
       <c r="P562" t="inlineStr"/>
+      <c r="Q562" t="inlineStr"/>
+      <c r="R562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -28859,6 +29991,8 @@
       <c r="N563" t="inlineStr"/>
       <c r="O563" t="inlineStr"/>
       <c r="P563" t="inlineStr"/>
+      <c r="Q563" t="inlineStr"/>
+      <c r="R563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -28909,6 +30043,8 @@
       <c r="N564" t="inlineStr"/>
       <c r="O564" t="inlineStr"/>
       <c r="P564" t="inlineStr"/>
+      <c r="Q564" t="inlineStr"/>
+      <c r="R564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -28959,6 +30095,8 @@
       <c r="N565" t="inlineStr"/>
       <c r="O565" t="inlineStr"/>
       <c r="P565" t="inlineStr"/>
+      <c r="Q565" t="inlineStr"/>
+      <c r="R565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -29009,6 +30147,8 @@
       <c r="N566" t="inlineStr"/>
       <c r="O566" t="inlineStr"/>
       <c r="P566" t="inlineStr"/>
+      <c r="Q566" t="inlineStr"/>
+      <c r="R566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -29059,6 +30199,8 @@
       <c r="N567" t="inlineStr"/>
       <c r="O567" t="inlineStr"/>
       <c r="P567" t="inlineStr"/>
+      <c r="Q567" t="inlineStr"/>
+      <c r="R567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -29109,6 +30251,8 @@
       <c r="N568" t="inlineStr"/>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="inlineStr"/>
+      <c r="Q568" t="inlineStr"/>
+      <c r="R568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -29159,6 +30303,8 @@
       <c r="N569" t="inlineStr"/>
       <c r="O569" t="inlineStr"/>
       <c r="P569" t="inlineStr"/>
+      <c r="Q569" t="inlineStr"/>
+      <c r="R569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -29209,6 +30355,8 @@
       <c r="N570" t="inlineStr"/>
       <c r="O570" t="inlineStr"/>
       <c r="P570" t="inlineStr"/>
+      <c r="Q570" t="inlineStr"/>
+      <c r="R570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -29259,6 +30407,8 @@
       <c r="N571" t="inlineStr"/>
       <c r="O571" t="inlineStr"/>
       <c r="P571" t="inlineStr"/>
+      <c r="Q571" t="inlineStr"/>
+      <c r="R571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -29309,6 +30459,8 @@
       <c r="N572" t="inlineStr"/>
       <c r="O572" t="inlineStr"/>
       <c r="P572" t="inlineStr"/>
+      <c r="Q572" t="inlineStr"/>
+      <c r="R572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -29359,6 +30511,8 @@
       <c r="N573" t="inlineStr"/>
       <c r="O573" t="inlineStr"/>
       <c r="P573" t="inlineStr"/>
+      <c r="Q573" t="inlineStr"/>
+      <c r="R573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -29409,6 +30563,8 @@
       <c r="N574" t="inlineStr"/>
       <c r="O574" t="inlineStr"/>
       <c r="P574" t="inlineStr"/>
+      <c r="Q574" t="inlineStr"/>
+      <c r="R574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -29459,6 +30615,8 @@
       <c r="N575" t="inlineStr"/>
       <c r="O575" t="inlineStr"/>
       <c r="P575" t="inlineStr"/>
+      <c r="Q575" t="inlineStr"/>
+      <c r="R575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -29509,6 +30667,8 @@
       <c r="N576" t="inlineStr"/>
       <c r="O576" t="inlineStr"/>
       <c r="P576" t="inlineStr"/>
+      <c r="Q576" t="inlineStr"/>
+      <c r="R576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -29559,6 +30719,8 @@
       <c r="N577" t="inlineStr"/>
       <c r="O577" t="inlineStr"/>
       <c r="P577" t="inlineStr"/>
+      <c r="Q577" t="inlineStr"/>
+      <c r="R577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -29609,6 +30771,8 @@
       <c r="N578" t="inlineStr"/>
       <c r="O578" t="inlineStr"/>
       <c r="P578" t="inlineStr"/>
+      <c r="Q578" t="inlineStr"/>
+      <c r="R578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -29659,6 +30823,8 @@
       <c r="N579" t="inlineStr"/>
       <c r="O579" t="inlineStr"/>
       <c r="P579" t="inlineStr"/>
+      <c r="Q579" t="inlineStr"/>
+      <c r="R579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -29709,6 +30875,8 @@
       <c r="N580" t="inlineStr"/>
       <c r="O580" t="inlineStr"/>
       <c r="P580" t="inlineStr"/>
+      <c r="Q580" t="inlineStr"/>
+      <c r="R580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -29759,6 +30927,8 @@
       <c r="N581" t="inlineStr"/>
       <c r="O581" t="inlineStr"/>
       <c r="P581" t="inlineStr"/>
+      <c r="Q581" t="inlineStr"/>
+      <c r="R581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -29807,6 +30977,8 @@
       <c r="N582" t="inlineStr"/>
       <c r="O582" t="inlineStr"/>
       <c r="P582" t="inlineStr"/>
+      <c r="Q582" t="inlineStr"/>
+      <c r="R582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -29855,6 +31027,8 @@
       <c r="N583" t="inlineStr"/>
       <c r="O583" t="inlineStr"/>
       <c r="P583" t="inlineStr"/>
+      <c r="Q583" t="inlineStr"/>
+      <c r="R583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -29903,6 +31077,8 @@
       <c r="N584" t="inlineStr"/>
       <c r="O584" t="inlineStr"/>
       <c r="P584" t="inlineStr"/>
+      <c r="Q584" t="inlineStr"/>
+      <c r="R584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -29951,6 +31127,8 @@
       <c r="N585" t="inlineStr"/>
       <c r="O585" t="inlineStr"/>
       <c r="P585" t="inlineStr"/>
+      <c r="Q585" t="inlineStr"/>
+      <c r="R585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -29999,6 +31177,8 @@
       <c r="N586" t="inlineStr"/>
       <c r="O586" t="inlineStr"/>
       <c r="P586" t="inlineStr"/>
+      <c r="Q586" t="inlineStr"/>
+      <c r="R586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -30047,6 +31227,8 @@
       <c r="N587" t="inlineStr"/>
       <c r="O587" t="inlineStr"/>
       <c r="P587" t="inlineStr"/>
+      <c r="Q587" t="inlineStr"/>
+      <c r="R587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -30095,6 +31277,8 @@
       <c r="N588" t="inlineStr"/>
       <c r="O588" t="inlineStr"/>
       <c r="P588" t="inlineStr"/>
+      <c r="Q588" t="inlineStr"/>
+      <c r="R588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -30143,6 +31327,8 @@
       <c r="N589" t="inlineStr"/>
       <c r="O589" t="inlineStr"/>
       <c r="P589" t="inlineStr"/>
+      <c r="Q589" t="inlineStr"/>
+      <c r="R589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -30191,6 +31377,8 @@
       <c r="N590" t="inlineStr"/>
       <c r="O590" t="inlineStr"/>
       <c r="P590" t="inlineStr"/>
+      <c r="Q590" t="inlineStr"/>
+      <c r="R590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -30239,6 +31427,8 @@
       <c r="N591" t="inlineStr"/>
       <c r="O591" t="inlineStr"/>
       <c r="P591" t="inlineStr"/>
+      <c r="Q591" t="inlineStr"/>
+      <c r="R591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -30287,6 +31477,8 @@
       <c r="N592" t="inlineStr"/>
       <c r="O592" t="inlineStr"/>
       <c r="P592" t="inlineStr"/>
+      <c r="Q592" t="inlineStr"/>
+      <c r="R592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -30335,6 +31527,8 @@
       <c r="N593" t="inlineStr"/>
       <c r="O593" t="inlineStr"/>
       <c r="P593" t="inlineStr"/>
+      <c r="Q593" t="inlineStr"/>
+      <c r="R593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -30383,6 +31577,8 @@
       <c r="N594" t="inlineStr"/>
       <c r="O594" t="inlineStr"/>
       <c r="P594" t="inlineStr"/>
+      <c r="Q594" t="inlineStr"/>
+      <c r="R594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -30431,6 +31627,8 @@
       <c r="N595" t="inlineStr"/>
       <c r="O595" t="inlineStr"/>
       <c r="P595" t="inlineStr"/>
+      <c r="Q595" t="inlineStr"/>
+      <c r="R595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -30479,6 +31677,8 @@
       <c r="N596" t="inlineStr"/>
       <c r="O596" t="inlineStr"/>
       <c r="P596" t="inlineStr"/>
+      <c r="Q596" t="inlineStr"/>
+      <c r="R596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -30527,6 +31727,8 @@
       <c r="N597" t="inlineStr"/>
       <c r="O597" t="inlineStr"/>
       <c r="P597" t="inlineStr"/>
+      <c r="Q597" t="inlineStr"/>
+      <c r="R597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -30575,6 +31777,8 @@
       <c r="N598" t="inlineStr"/>
       <c r="O598" t="inlineStr"/>
       <c r="P598" t="inlineStr"/>
+      <c r="Q598" t="inlineStr"/>
+      <c r="R598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -30623,6 +31827,8 @@
       <c r="N599" t="inlineStr"/>
       <c r="O599" t="inlineStr"/>
       <c r="P599" t="inlineStr"/>
+      <c r="Q599" t="inlineStr"/>
+      <c r="R599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -30671,6 +31877,8 @@
       <c r="N600" t="inlineStr"/>
       <c r="O600" t="inlineStr"/>
       <c r="P600" t="inlineStr"/>
+      <c r="Q600" t="inlineStr"/>
+      <c r="R600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -30719,6 +31927,8 @@
       <c r="N601" t="inlineStr"/>
       <c r="O601" t="inlineStr"/>
       <c r="P601" t="inlineStr"/>
+      <c r="Q601" t="inlineStr"/>
+      <c r="R601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -30767,6 +31977,8 @@
       <c r="N602" t="inlineStr"/>
       <c r="O602" t="inlineStr"/>
       <c r="P602" t="inlineStr"/>
+      <c r="Q602" t="inlineStr"/>
+      <c r="R602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -30815,6 +32027,8 @@
       <c r="N603" t="inlineStr"/>
       <c r="O603" t="inlineStr"/>
       <c r="P603" t="inlineStr"/>
+      <c r="Q603" t="inlineStr"/>
+      <c r="R603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -30863,6 +32077,8 @@
       <c r="N604" t="inlineStr"/>
       <c r="O604" t="inlineStr"/>
       <c r="P604" t="inlineStr"/>
+      <c r="Q604" t="inlineStr"/>
+      <c r="R604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -30911,6 +32127,8 @@
       <c r="N605" t="inlineStr"/>
       <c r="O605" t="inlineStr"/>
       <c r="P605" t="inlineStr"/>
+      <c r="Q605" t="inlineStr"/>
+      <c r="R605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -30959,6 +32177,8 @@
       <c r="N606" t="inlineStr"/>
       <c r="O606" t="inlineStr"/>
       <c r="P606" t="inlineStr"/>
+      <c r="Q606" t="inlineStr"/>
+      <c r="R606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -31003,6 +32223,8 @@
       <c r="N607" t="inlineStr"/>
       <c r="O607" t="inlineStr"/>
       <c r="P607" t="inlineStr"/>
+      <c r="Q607" t="inlineStr"/>
+      <c r="R607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -31051,6 +32273,8 @@
       <c r="N608" t="inlineStr"/>
       <c r="O608" t="inlineStr"/>
       <c r="P608" t="inlineStr"/>
+      <c r="Q608" t="inlineStr"/>
+      <c r="R608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -31099,6 +32323,8 @@
       <c r="N609" t="inlineStr"/>
       <c r="O609" t="inlineStr"/>
       <c r="P609" t="inlineStr"/>
+      <c r="Q609" t="inlineStr"/>
+      <c r="R609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -31147,6 +32373,8 @@
       <c r="N610" t="inlineStr"/>
       <c r="O610" t="inlineStr"/>
       <c r="P610" t="inlineStr"/>
+      <c r="Q610" t="inlineStr"/>
+      <c r="R610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -31195,6 +32423,8 @@
       <c r="N611" t="inlineStr"/>
       <c r="O611" t="inlineStr"/>
       <c r="P611" t="inlineStr"/>
+      <c r="Q611" t="inlineStr"/>
+      <c r="R611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -31243,6 +32473,8 @@
       <c r="N612" t="inlineStr"/>
       <c r="O612" t="inlineStr"/>
       <c r="P612" t="inlineStr"/>
+      <c r="Q612" t="inlineStr"/>
+      <c r="R612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -31291,6 +32523,8 @@
       <c r="N613" t="inlineStr"/>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="inlineStr"/>
+      <c r="Q613" t="inlineStr"/>
+      <c r="R613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -31339,6 +32573,8 @@
       <c r="N614" t="inlineStr"/>
       <c r="O614" t="inlineStr"/>
       <c r="P614" t="inlineStr"/>
+      <c r="Q614" t="inlineStr"/>
+      <c r="R614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -31387,6 +32623,8 @@
       <c r="N615" t="inlineStr"/>
       <c r="O615" t="inlineStr"/>
       <c r="P615" t="inlineStr"/>
+      <c r="Q615" t="inlineStr"/>
+      <c r="R615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -31435,6 +32673,8 @@
       <c r="N616" t="inlineStr"/>
       <c r="O616" t="inlineStr"/>
       <c r="P616" t="inlineStr"/>
+      <c r="Q616" t="inlineStr"/>
+      <c r="R616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -31483,6 +32723,8 @@
       <c r="N617" t="inlineStr"/>
       <c r="O617" t="inlineStr"/>
       <c r="P617" t="inlineStr"/>
+      <c r="Q617" t="inlineStr"/>
+      <c r="R617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -31531,6 +32773,8 @@
       <c r="N618" t="inlineStr"/>
       <c r="O618" t="inlineStr"/>
       <c r="P618" t="inlineStr"/>
+      <c r="Q618" t="inlineStr"/>
+      <c r="R618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -31579,6 +32823,8 @@
       <c r="N619" t="inlineStr"/>
       <c r="O619" t="inlineStr"/>
       <c r="P619" t="inlineStr"/>
+      <c r="Q619" t="inlineStr"/>
+      <c r="R619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -31627,6 +32873,8 @@
       <c r="N620" t="inlineStr"/>
       <c r="O620" t="inlineStr"/>
       <c r="P620" t="inlineStr"/>
+      <c r="Q620" t="inlineStr"/>
+      <c r="R620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -31675,6 +32923,8 @@
       <c r="N621" t="inlineStr"/>
       <c r="O621" t="inlineStr"/>
       <c r="P621" t="inlineStr"/>
+      <c r="Q621" t="inlineStr"/>
+      <c r="R621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -31723,6 +32973,8 @@
       <c r="N622" t="inlineStr"/>
       <c r="O622" t="inlineStr"/>
       <c r="P622" t="inlineStr"/>
+      <c r="Q622" t="inlineStr"/>
+      <c r="R622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -31771,6 +33023,8 @@
       <c r="N623" t="inlineStr"/>
       <c r="O623" t="inlineStr"/>
       <c r="P623" t="inlineStr"/>
+      <c r="Q623" t="inlineStr"/>
+      <c r="R623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -31819,6 +33073,8 @@
       <c r="N624" t="inlineStr"/>
       <c r="O624" t="inlineStr"/>
       <c r="P624" t="inlineStr"/>
+      <c r="Q624" t="inlineStr"/>
+      <c r="R624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -31867,6 +33123,8 @@
       <c r="N625" t="inlineStr"/>
       <c r="O625" t="inlineStr"/>
       <c r="P625" t="inlineStr"/>
+      <c r="Q625" t="inlineStr"/>
+      <c r="R625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -31915,6 +33173,8 @@
       <c r="N626" t="inlineStr"/>
       <c r="O626" t="inlineStr"/>
       <c r="P626" t="inlineStr"/>
+      <c r="Q626" t="inlineStr"/>
+      <c r="R626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -31963,6 +33223,8 @@
       <c r="N627" t="inlineStr"/>
       <c r="O627" t="inlineStr"/>
       <c r="P627" t="inlineStr"/>
+      <c r="Q627" t="inlineStr"/>
+      <c r="R627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -32011,6 +33273,8 @@
       <c r="N628" t="inlineStr"/>
       <c r="O628" t="inlineStr"/>
       <c r="P628" t="inlineStr"/>
+      <c r="Q628" t="inlineStr"/>
+      <c r="R628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -32059,6 +33323,8 @@
       <c r="N629" t="inlineStr"/>
       <c r="O629" t="inlineStr"/>
       <c r="P629" t="inlineStr"/>
+      <c r="Q629" t="inlineStr"/>
+      <c r="R629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -32107,6 +33373,8 @@
       <c r="N630" t="inlineStr"/>
       <c r="O630" t="inlineStr"/>
       <c r="P630" t="inlineStr"/>
+      <c r="Q630" t="inlineStr"/>
+      <c r="R630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -32155,6 +33423,8 @@
       <c r="N631" t="inlineStr"/>
       <c r="O631" t="inlineStr"/>
       <c r="P631" t="inlineStr"/>
+      <c r="Q631" t="inlineStr"/>
+      <c r="R631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -32203,6 +33473,8 @@
       <c r="N632" t="inlineStr"/>
       <c r="O632" t="inlineStr"/>
       <c r="P632" t="inlineStr"/>
+      <c r="Q632" t="inlineStr"/>
+      <c r="R632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -32251,6 +33523,8 @@
       <c r="N633" t="inlineStr"/>
       <c r="O633" t="inlineStr"/>
       <c r="P633" t="inlineStr"/>
+      <c r="Q633" t="inlineStr"/>
+      <c r="R633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -32299,6 +33573,8 @@
       <c r="N634" t="inlineStr"/>
       <c r="O634" t="inlineStr"/>
       <c r="P634" t="inlineStr"/>
+      <c r="Q634" t="inlineStr"/>
+      <c r="R634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -32347,6 +33623,8 @@
       <c r="N635" t="inlineStr"/>
       <c r="O635" t="inlineStr"/>
       <c r="P635" t="inlineStr"/>
+      <c r="Q635" t="inlineStr"/>
+      <c r="R635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -32395,6 +33673,8 @@
       <c r="N636" t="inlineStr"/>
       <c r="O636" t="inlineStr"/>
       <c r="P636" t="inlineStr"/>
+      <c r="Q636" t="inlineStr"/>
+      <c r="R636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -32443,6 +33723,8 @@
       <c r="N637" t="inlineStr"/>
       <c r="O637" t="inlineStr"/>
       <c r="P637" t="inlineStr"/>
+      <c r="Q637" t="inlineStr"/>
+      <c r="R637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -32491,6 +33773,8 @@
       <c r="N638" t="inlineStr"/>
       <c r="O638" t="inlineStr"/>
       <c r="P638" t="inlineStr"/>
+      <c r="Q638" t="inlineStr"/>
+      <c r="R638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -32539,6 +33823,8 @@
       <c r="N639" t="inlineStr"/>
       <c r="O639" t="inlineStr"/>
       <c r="P639" t="inlineStr"/>
+      <c r="Q639" t="inlineStr"/>
+      <c r="R639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -32587,6 +33873,8 @@
       <c r="N640" t="inlineStr"/>
       <c r="O640" t="inlineStr"/>
       <c r="P640" t="inlineStr"/>
+      <c r="Q640" t="inlineStr"/>
+      <c r="R640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -32635,6 +33923,8 @@
       <c r="N641" t="inlineStr"/>
       <c r="O641" t="inlineStr"/>
       <c r="P641" t="inlineStr"/>
+      <c r="Q641" t="inlineStr"/>
+      <c r="R641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -32683,6 +33973,8 @@
       <c r="N642" t="inlineStr"/>
       <c r="O642" t="inlineStr"/>
       <c r="P642" t="inlineStr"/>
+      <c r="Q642" t="inlineStr"/>
+      <c r="R642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -32731,6 +34023,8 @@
       <c r="N643" t="inlineStr"/>
       <c r="O643" t="inlineStr"/>
       <c r="P643" t="inlineStr"/>
+      <c r="Q643" t="inlineStr"/>
+      <c r="R643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -32779,6 +34073,8 @@
       <c r="N644" t="inlineStr"/>
       <c r="O644" t="inlineStr"/>
       <c r="P644" t="inlineStr"/>
+      <c r="Q644" t="inlineStr"/>
+      <c r="R644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -32827,6 +34123,8 @@
       <c r="N645" t="inlineStr"/>
       <c r="O645" t="inlineStr"/>
       <c r="P645" t="inlineStr"/>
+      <c r="Q645" t="inlineStr"/>
+      <c r="R645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -32875,6 +34173,8 @@
       <c r="N646" t="inlineStr"/>
       <c r="O646" t="inlineStr"/>
       <c r="P646" t="inlineStr"/>
+      <c r="Q646" t="inlineStr"/>
+      <c r="R646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -32923,6 +34223,8 @@
       <c r="N647" t="inlineStr"/>
       <c r="O647" t="inlineStr"/>
       <c r="P647" t="inlineStr"/>
+      <c r="Q647" t="inlineStr"/>
+      <c r="R647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -32971,6 +34273,8 @@
       <c r="N648" t="inlineStr"/>
       <c r="O648" t="inlineStr"/>
       <c r="P648" t="inlineStr"/>
+      <c r="Q648" t="inlineStr"/>
+      <c r="R648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -33019,6 +34323,8 @@
       <c r="N649" t="inlineStr"/>
       <c r="O649" t="inlineStr"/>
       <c r="P649" t="inlineStr"/>
+      <c r="Q649" t="inlineStr"/>
+      <c r="R649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -33067,6 +34373,8 @@
       <c r="N650" t="inlineStr"/>
       <c r="O650" t="inlineStr"/>
       <c r="P650" t="inlineStr"/>
+      <c r="Q650" t="inlineStr"/>
+      <c r="R650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -33115,6 +34423,8 @@
       <c r="N651" t="inlineStr"/>
       <c r="O651" t="inlineStr"/>
       <c r="P651" t="inlineStr"/>
+      <c r="Q651" t="inlineStr"/>
+      <c r="R651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -33163,6 +34473,8 @@
       <c r="N652" t="inlineStr"/>
       <c r="O652" t="inlineStr"/>
       <c r="P652" t="inlineStr"/>
+      <c r="Q652" t="inlineStr"/>
+      <c r="R652" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_uz_asesoramiento.xlsx
+++ b/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_uz_asesoramiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R652"/>
+  <dimension ref="A1:S652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +505,11 @@
       <c r="R1" t="inlineStr">
         <is>
           <t>ugel</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
@@ -563,6 +568,11 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -619,6 +629,11 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -675,6 +690,11 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -731,6 +751,11 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -787,6 +812,11 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -843,6 +873,11 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -899,6 +934,11 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -955,6 +995,11 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1011,6 +1056,11 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1067,6 +1117,11 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1123,6 +1178,11 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1179,6 +1239,11 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1235,6 +1300,11 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1291,6 +1361,11 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1347,6 +1422,11 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1403,6 +1483,11 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1455,6 +1540,11 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1511,6 +1601,11 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1559,6 +1654,11 @@
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1615,6 +1715,11 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1671,6 +1776,11 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1727,6 +1837,11 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1783,6 +1898,11 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1839,6 +1959,11 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1895,6 +2020,11 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1951,6 +2081,11 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2007,6 +2142,11 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2063,6 +2203,11 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2119,6 +2264,11 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2175,6 +2325,11 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2231,6 +2386,11 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2287,6 +2447,11 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2343,6 +2508,11 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2399,6 +2569,11 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2455,6 +2630,11 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2511,6 +2691,11 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2567,6 +2752,11 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2621,6 +2811,11 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2677,6 +2872,11 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2733,6 +2933,11 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2789,6 +2994,11 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2845,6 +3055,11 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2901,6 +3116,11 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2957,6 +3177,11 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3013,6 +3238,11 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3069,6 +3299,11 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3125,6 +3360,11 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3181,6 +3421,11 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3237,6 +3482,11 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3293,6 +3543,11 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3345,6 +3600,11 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3401,6 +3661,11 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3457,6 +3722,11 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3513,6 +3783,11 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3569,6 +3844,11 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3625,6 +3905,11 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3681,6 +3966,11 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3737,6 +4027,11 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3793,6 +4088,11 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3849,6 +4149,11 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3905,6 +4210,11 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3959,6 +4269,11 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4015,6 +4330,11 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4071,6 +4391,11 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4127,6 +4452,11 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4183,6 +4513,11 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4239,6 +4574,11 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4295,6 +4635,11 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4351,6 +4696,11 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4405,6 +4755,11 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4459,6 +4814,11 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4513,6 +4873,11 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4567,6 +4932,11 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4621,6 +4991,11 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4675,6 +5050,11 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4725,6 +5105,11 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4775,6 +5160,11 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4825,6 +5215,11 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4875,6 +5270,11 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4929,6 +5329,11 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4983,6 +5388,11 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5037,6 +5447,11 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5091,6 +5506,11 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5145,6 +5565,11 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5195,6 +5620,11 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5241,6 +5671,11 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5295,6 +5730,11 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5349,6 +5789,11 @@
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5403,6 +5848,11 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5457,6 +5907,11 @@
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5511,6 +5966,11 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5561,6 +6021,11 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5617,6 +6082,11 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5669,6 +6139,11 @@
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5721,6 +6196,11 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5777,6 +6257,11 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5833,6 +6318,11 @@
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5889,6 +6379,11 @@
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5945,6 +6440,11 @@
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6001,6 +6501,11 @@
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6053,6 +6558,11 @@
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6105,6 +6615,11 @@
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6157,6 +6672,11 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6205,6 +6725,11 @@
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6259,6 +6784,11 @@
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6313,6 +6843,11 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6367,6 +6902,11 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6421,6 +6961,11 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6475,6 +7020,11 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6529,6 +7079,11 @@
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6583,6 +7138,11 @@
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6637,6 +7197,11 @@
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6687,6 +7252,11 @@
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6737,6 +7307,11 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6787,6 +7362,11 @@
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6841,6 +7421,11 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6895,6 +7480,11 @@
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6949,6 +7539,11 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7003,6 +7598,11 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7049,6 +7649,11 @@
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7095,6 +7700,11 @@
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7141,6 +7751,11 @@
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7187,6 +7802,11 @@
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7229,6 +7849,11 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7271,6 +7896,11 @@
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7317,6 +7947,11 @@
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7363,6 +7998,11 @@
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7409,6 +8049,11 @@
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7455,6 +8100,11 @@
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7501,6 +8151,11 @@
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7557,6 +8212,11 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7613,6 +8273,11 @@
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7669,6 +8334,11 @@
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7725,6 +8395,11 @@
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7781,6 +8456,11 @@
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7835,6 +8515,11 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7891,6 +8576,11 @@
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -7947,6 +8637,11 @@
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8003,6 +8698,11 @@
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8059,6 +8759,11 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8115,6 +8820,11 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8171,6 +8881,11 @@
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8223,6 +8938,11 @@
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8279,6 +8999,11 @@
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8331,6 +9056,11 @@
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8387,6 +9117,11 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8439,6 +9174,11 @@
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8495,6 +9235,11 @@
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8551,6 +9296,11 @@
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8607,6 +9357,11 @@
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8663,6 +9418,11 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8719,6 +9479,11 @@
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8775,6 +9540,11 @@
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8831,6 +9601,11 @@
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8887,6 +9662,11 @@
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8943,6 +9723,11 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8999,6 +9784,11 @@
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9051,6 +9841,11 @@
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9103,6 +9898,11 @@
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9155,6 +9955,11 @@
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9207,6 +10012,11 @@
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9259,6 +10069,11 @@
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9311,6 +10126,11 @@
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9363,6 +10183,11 @@
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9415,6 +10240,11 @@
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9467,6 +10297,11 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9519,6 +10354,11 @@
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -9571,6 +10411,11 @@
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -9623,6 +10468,11 @@
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9675,6 +10525,11 @@
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -9727,6 +10582,11 @@
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9779,6 +10639,11 @@
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -9831,6 +10696,11 @@
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -9883,6 +10753,11 @@
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9935,6 +10810,11 @@
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9987,6 +10867,11 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10039,6 +10924,11 @@
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10091,6 +10981,11 @@
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10143,6 +11038,11 @@
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10195,6 +11095,11 @@
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10247,6 +11152,11 @@
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -10299,6 +11209,11 @@
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -10351,6 +11266,11 @@
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10403,6 +11323,11 @@
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -10455,6 +11380,11 @@
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -10507,6 +11437,11 @@
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -10559,6 +11494,11 @@
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -10611,6 +11551,11 @@
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -10663,6 +11608,11 @@
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -10715,6 +11665,11 @@
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -10767,6 +11722,11 @@
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -10817,6 +11777,11 @@
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -10867,6 +11832,11 @@
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -10917,6 +11887,11 @@
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -10967,6 +11942,11 @@
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11017,6 +11997,11 @@
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11067,6 +12052,11 @@
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -11117,6 +12107,11 @@
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -11167,6 +12162,11 @@
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -11217,6 +12217,11 @@
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -11267,6 +12272,11 @@
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -11317,6 +12327,11 @@
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -11367,6 +12382,11 @@
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr"/>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -11419,6 +12439,11 @@
       <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -11471,6 +12496,11 @@
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -11523,6 +12553,11 @@
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -11575,6 +12610,11 @@
       <c r="P208" t="inlineStr"/>
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -11627,6 +12667,11 @@
       <c r="P209" t="inlineStr"/>
       <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -11679,6 +12724,11 @@
       <c r="P210" t="inlineStr"/>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -11731,6 +12781,11 @@
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -11783,6 +12838,11 @@
       <c r="P212" t="inlineStr"/>
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -11835,6 +12895,11 @@
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -11887,6 +12952,11 @@
       <c r="P214" t="inlineStr"/>
       <c r="Q214" t="inlineStr"/>
       <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -11939,6 +13009,11 @@
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr"/>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -11991,6 +13066,11 @@
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -12043,6 +13123,11 @@
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -12093,6 +13178,11 @@
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -12143,6 +13233,11 @@
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -12193,6 +13288,11 @@
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -12245,6 +13345,11 @@
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -12297,6 +13402,11 @@
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -12347,6 +13457,11 @@
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -12397,6 +13512,11 @@
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr"/>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -12447,6 +13567,11 @@
       <c r="P225" t="inlineStr"/>
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr"/>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -12495,6 +13620,11 @@
       <c r="P226" t="inlineStr"/>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -12547,6 +13677,11 @@
       <c r="P227" t="inlineStr"/>
       <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -12599,6 +13734,11 @@
       <c r="P228" t="inlineStr"/>
       <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr"/>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -12651,6 +13791,11 @@
       <c r="P229" t="inlineStr"/>
       <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr"/>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -12701,6 +13846,11 @@
       <c r="P230" t="inlineStr"/>
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -12751,6 +13901,11 @@
       <c r="P231" t="inlineStr"/>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -12801,6 +13956,11 @@
       <c r="P232" t="inlineStr"/>
       <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr"/>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -12851,6 +14011,11 @@
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr"/>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -12903,6 +14068,11 @@
       <c r="P234" t="inlineStr"/>
       <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr"/>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -12955,6 +14125,11 @@
       <c r="P235" t="inlineStr"/>
       <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr"/>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -13005,6 +14180,11 @@
       <c r="P236" t="inlineStr"/>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr"/>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -13055,6 +14235,11 @@
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr"/>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -13107,6 +14292,11 @@
       <c r="P238" t="inlineStr"/>
       <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr"/>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -13159,6 +14349,11 @@
       <c r="P239" t="inlineStr"/>
       <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -13211,6 +14406,11 @@
       <c r="P240" t="inlineStr"/>
       <c r="Q240" t="inlineStr"/>
       <c r="R240" t="inlineStr"/>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -13263,6 +14463,11 @@
       <c r="P241" t="inlineStr"/>
       <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr"/>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -13315,6 +14520,11 @@
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr"/>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -13367,6 +14577,11 @@
       <c r="P243" t="inlineStr"/>
       <c r="Q243" t="inlineStr"/>
       <c r="R243" t="inlineStr"/>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -13417,6 +14632,11 @@
       <c r="P244" t="inlineStr"/>
       <c r="Q244" t="inlineStr"/>
       <c r="R244" t="inlineStr"/>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -13469,6 +14689,11 @@
       <c r="P245" t="inlineStr"/>
       <c r="Q245" t="inlineStr"/>
       <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -13519,6 +14744,11 @@
       <c r="P246" t="inlineStr"/>
       <c r="Q246" t="inlineStr"/>
       <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -13571,6 +14801,11 @@
       <c r="P247" t="inlineStr"/>
       <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr"/>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -13621,6 +14856,11 @@
       <c r="P248" t="inlineStr"/>
       <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr"/>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -13673,6 +14913,11 @@
       <c r="P249" t="inlineStr"/>
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr"/>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -13723,6 +14968,11 @@
       <c r="P250" t="inlineStr"/>
       <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr"/>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -13775,6 +15025,11 @@
       <c r="P251" t="inlineStr"/>
       <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr"/>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -13825,6 +15080,11 @@
       <c r="P252" t="inlineStr"/>
       <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr"/>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -13873,6 +15133,11 @@
       <c r="P253" t="inlineStr"/>
       <c r="Q253" t="inlineStr"/>
       <c r="R253" t="inlineStr"/>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -13925,6 +15190,11 @@
       <c r="P254" t="inlineStr"/>
       <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr"/>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -13977,6 +15247,11 @@
       <c r="P255" t="inlineStr"/>
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr"/>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -14029,6 +15304,11 @@
       <c r="P256" t="inlineStr"/>
       <c r="Q256" t="inlineStr"/>
       <c r="R256" t="inlineStr"/>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -14081,6 +15361,11 @@
       <c r="P257" t="inlineStr"/>
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr"/>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -14133,6 +15418,11 @@
       <c r="P258" t="inlineStr"/>
       <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr"/>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -14185,6 +15475,11 @@
       <c r="P259" t="inlineStr"/>
       <c r="Q259" t="inlineStr"/>
       <c r="R259" t="inlineStr"/>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -14237,6 +15532,11 @@
       <c r="P260" t="inlineStr"/>
       <c r="Q260" t="inlineStr"/>
       <c r="R260" t="inlineStr"/>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -14289,6 +15589,11 @@
       <c r="P261" t="inlineStr"/>
       <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -14341,6 +15646,11 @@
       <c r="P262" t="inlineStr"/>
       <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr"/>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -14393,6 +15703,11 @@
       <c r="P263" t="inlineStr"/>
       <c r="Q263" t="inlineStr"/>
       <c r="R263" t="inlineStr"/>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -14445,6 +15760,11 @@
       <c r="P264" t="inlineStr"/>
       <c r="Q264" t="inlineStr"/>
       <c r="R264" t="inlineStr"/>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -14497,6 +15817,11 @@
       <c r="P265" t="inlineStr"/>
       <c r="Q265" t="inlineStr"/>
       <c r="R265" t="inlineStr"/>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -14549,6 +15874,11 @@
       <c r="P266" t="inlineStr"/>
       <c r="Q266" t="inlineStr"/>
       <c r="R266" t="inlineStr"/>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -14601,6 +15931,11 @@
       <c r="P267" t="inlineStr"/>
       <c r="Q267" t="inlineStr"/>
       <c r="R267" t="inlineStr"/>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -14653,6 +15988,11 @@
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="inlineStr"/>
       <c r="R268" t="inlineStr"/>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -14705,6 +16045,11 @@
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="inlineStr"/>
       <c r="R269" t="inlineStr"/>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -14757,6 +16102,11 @@
       <c r="P270" t="inlineStr"/>
       <c r="Q270" t="inlineStr"/>
       <c r="R270" t="inlineStr"/>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -14809,6 +16159,11 @@
       <c r="P271" t="inlineStr"/>
       <c r="Q271" t="inlineStr"/>
       <c r="R271" t="inlineStr"/>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -14861,6 +16216,11 @@
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="inlineStr"/>
       <c r="R272" t="inlineStr"/>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -14913,6 +16273,11 @@
       <c r="P273" t="inlineStr"/>
       <c r="Q273" t="inlineStr"/>
       <c r="R273" t="inlineStr"/>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -14965,6 +16330,11 @@
       <c r="P274" t="inlineStr"/>
       <c r="Q274" t="inlineStr"/>
       <c r="R274" t="inlineStr"/>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -15017,6 +16387,11 @@
       <c r="P275" t="inlineStr"/>
       <c r="Q275" t="inlineStr"/>
       <c r="R275" t="inlineStr"/>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -15069,6 +16444,11 @@
       <c r="P276" t="inlineStr"/>
       <c r="Q276" t="inlineStr"/>
       <c r="R276" t="inlineStr"/>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -15121,6 +16501,11 @@
       <c r="P277" t="inlineStr"/>
       <c r="Q277" t="inlineStr"/>
       <c r="R277" t="inlineStr"/>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -15173,6 +16558,11 @@
       <c r="P278" t="inlineStr"/>
       <c r="Q278" t="inlineStr"/>
       <c r="R278" t="inlineStr"/>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -15225,6 +16615,11 @@
       <c r="P279" t="inlineStr"/>
       <c r="Q279" t="inlineStr"/>
       <c r="R279" t="inlineStr"/>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -15277,6 +16672,11 @@
       <c r="P280" t="inlineStr"/>
       <c r="Q280" t="inlineStr"/>
       <c r="R280" t="inlineStr"/>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -15329,6 +16729,11 @@
       <c r="P281" t="inlineStr"/>
       <c r="Q281" t="inlineStr"/>
       <c r="R281" t="inlineStr"/>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -15381,6 +16786,11 @@
       <c r="P282" t="inlineStr"/>
       <c r="Q282" t="inlineStr"/>
       <c r="R282" t="inlineStr"/>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -15433,6 +16843,11 @@
       <c r="P283" t="inlineStr"/>
       <c r="Q283" t="inlineStr"/>
       <c r="R283" t="inlineStr"/>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -15485,6 +16900,11 @@
       <c r="P284" t="inlineStr"/>
       <c r="Q284" t="inlineStr"/>
       <c r="R284" t="inlineStr"/>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -15537,6 +16957,11 @@
       <c r="P285" t="inlineStr"/>
       <c r="Q285" t="inlineStr"/>
       <c r="R285" t="inlineStr"/>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -15589,6 +17014,11 @@
       <c r="P286" t="inlineStr"/>
       <c r="Q286" t="inlineStr"/>
       <c r="R286" t="inlineStr"/>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -15641,6 +17071,11 @@
       <c r="P287" t="inlineStr"/>
       <c r="Q287" t="inlineStr"/>
       <c r="R287" t="inlineStr"/>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -15693,6 +17128,11 @@
       <c r="P288" t="inlineStr"/>
       <c r="Q288" t="inlineStr"/>
       <c r="R288" t="inlineStr"/>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -15745,6 +17185,11 @@
       <c r="P289" t="inlineStr"/>
       <c r="Q289" t="inlineStr"/>
       <c r="R289" t="inlineStr"/>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -15797,6 +17242,11 @@
       <c r="P290" t="inlineStr"/>
       <c r="Q290" t="inlineStr"/>
       <c r="R290" t="inlineStr"/>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -15849,6 +17299,11 @@
       <c r="P291" t="inlineStr"/>
       <c r="Q291" t="inlineStr"/>
       <c r="R291" t="inlineStr"/>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -15901,6 +17356,11 @@
       <c r="P292" t="inlineStr"/>
       <c r="Q292" t="inlineStr"/>
       <c r="R292" t="inlineStr"/>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -15953,6 +17413,11 @@
       <c r="P293" t="inlineStr"/>
       <c r="Q293" t="inlineStr"/>
       <c r="R293" t="inlineStr"/>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -16005,6 +17470,11 @@
       <c r="P294" t="inlineStr"/>
       <c r="Q294" t="inlineStr"/>
       <c r="R294" t="inlineStr"/>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -16057,6 +17527,11 @@
       <c r="P295" t="inlineStr"/>
       <c r="Q295" t="inlineStr"/>
       <c r="R295" t="inlineStr"/>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -16109,6 +17584,11 @@
       <c r="P296" t="inlineStr"/>
       <c r="Q296" t="inlineStr"/>
       <c r="R296" t="inlineStr"/>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -16161,6 +17641,11 @@
       <c r="P297" t="inlineStr"/>
       <c r="Q297" t="inlineStr"/>
       <c r="R297" t="inlineStr"/>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -16213,6 +17698,11 @@
       <c r="P298" t="inlineStr"/>
       <c r="Q298" t="inlineStr"/>
       <c r="R298" t="inlineStr"/>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -16265,6 +17755,11 @@
       <c r="P299" t="inlineStr"/>
       <c r="Q299" t="inlineStr"/>
       <c r="R299" t="inlineStr"/>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -16317,6 +17812,11 @@
       <c r="P300" t="inlineStr"/>
       <c r="Q300" t="inlineStr"/>
       <c r="R300" t="inlineStr"/>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -16369,6 +17869,11 @@
       <c r="P301" t="inlineStr"/>
       <c r="Q301" t="inlineStr"/>
       <c r="R301" t="inlineStr"/>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -16421,6 +17926,11 @@
       <c r="P302" t="inlineStr"/>
       <c r="Q302" t="inlineStr"/>
       <c r="R302" t="inlineStr"/>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -16473,6 +17983,11 @@
       <c r="P303" t="inlineStr"/>
       <c r="Q303" t="inlineStr"/>
       <c r="R303" t="inlineStr"/>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -16525,6 +18040,11 @@
       <c r="P304" t="inlineStr"/>
       <c r="Q304" t="inlineStr"/>
       <c r="R304" t="inlineStr"/>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -16577,6 +18097,11 @@
       <c r="P305" t="inlineStr"/>
       <c r="Q305" t="inlineStr"/>
       <c r="R305" t="inlineStr"/>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -16629,6 +18154,11 @@
       <c r="P306" t="inlineStr"/>
       <c r="Q306" t="inlineStr"/>
       <c r="R306" t="inlineStr"/>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -16681,6 +18211,11 @@
       <c r="P307" t="inlineStr"/>
       <c r="Q307" t="inlineStr"/>
       <c r="R307" t="inlineStr"/>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -16733,6 +18268,11 @@
       <c r="P308" t="inlineStr"/>
       <c r="Q308" t="inlineStr"/>
       <c r="R308" t="inlineStr"/>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -16785,6 +18325,11 @@
       <c r="P309" t="inlineStr"/>
       <c r="Q309" t="inlineStr"/>
       <c r="R309" t="inlineStr"/>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -16837,6 +18382,11 @@
       <c r="P310" t="inlineStr"/>
       <c r="Q310" t="inlineStr"/>
       <c r="R310" t="inlineStr"/>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -16889,6 +18439,11 @@
       <c r="P311" t="inlineStr"/>
       <c r="Q311" t="inlineStr"/>
       <c r="R311" t="inlineStr"/>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -16941,6 +18496,11 @@
       <c r="P312" t="inlineStr"/>
       <c r="Q312" t="inlineStr"/>
       <c r="R312" t="inlineStr"/>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -16993,6 +18553,11 @@
       <c r="P313" t="inlineStr"/>
       <c r="Q313" t="inlineStr"/>
       <c r="R313" t="inlineStr"/>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -17045,6 +18610,11 @@
       <c r="P314" t="inlineStr"/>
       <c r="Q314" t="inlineStr"/>
       <c r="R314" t="inlineStr"/>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -17097,6 +18667,11 @@
       <c r="P315" t="inlineStr"/>
       <c r="Q315" t="inlineStr"/>
       <c r="R315" t="inlineStr"/>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -17149,6 +18724,11 @@
       <c r="P316" t="inlineStr"/>
       <c r="Q316" t="inlineStr"/>
       <c r="R316" t="inlineStr"/>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -17201,6 +18781,11 @@
       <c r="P317" t="inlineStr"/>
       <c r="Q317" t="inlineStr"/>
       <c r="R317" t="inlineStr"/>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -17253,6 +18838,11 @@
       <c r="P318" t="inlineStr"/>
       <c r="Q318" t="inlineStr"/>
       <c r="R318" t="inlineStr"/>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -17305,6 +18895,11 @@
       <c r="P319" t="inlineStr"/>
       <c r="Q319" t="inlineStr"/>
       <c r="R319" t="inlineStr"/>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -17357,6 +18952,11 @@
       <c r="P320" t="inlineStr"/>
       <c r="Q320" t="inlineStr"/>
       <c r="R320" t="inlineStr"/>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -17409,6 +19009,11 @@
       <c r="P321" t="inlineStr"/>
       <c r="Q321" t="inlineStr"/>
       <c r="R321" t="inlineStr"/>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -17461,6 +19066,11 @@
       <c r="P322" t="inlineStr"/>
       <c r="Q322" t="inlineStr"/>
       <c r="R322" t="inlineStr"/>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -17513,6 +19123,11 @@
       <c r="P323" t="inlineStr"/>
       <c r="Q323" t="inlineStr"/>
       <c r="R323" t="inlineStr"/>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -17565,6 +19180,11 @@
       <c r="P324" t="inlineStr"/>
       <c r="Q324" t="inlineStr"/>
       <c r="R324" t="inlineStr"/>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -17617,6 +19237,11 @@
       <c r="P325" t="inlineStr"/>
       <c r="Q325" t="inlineStr"/>
       <c r="R325" t="inlineStr"/>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -17669,6 +19294,11 @@
       <c r="P326" t="inlineStr"/>
       <c r="Q326" t="inlineStr"/>
       <c r="R326" t="inlineStr"/>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -17721,6 +19351,11 @@
       <c r="P327" t="inlineStr"/>
       <c r="Q327" t="inlineStr"/>
       <c r="R327" t="inlineStr"/>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -17773,6 +19408,11 @@
       <c r="P328" t="inlineStr"/>
       <c r="Q328" t="inlineStr"/>
       <c r="R328" t="inlineStr"/>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -17825,6 +19465,11 @@
       <c r="P329" t="inlineStr"/>
       <c r="Q329" t="inlineStr"/>
       <c r="R329" t="inlineStr"/>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -17877,6 +19522,11 @@
       <c r="P330" t="inlineStr"/>
       <c r="Q330" t="inlineStr"/>
       <c r="R330" t="inlineStr"/>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -17929,6 +19579,11 @@
       <c r="P331" t="inlineStr"/>
       <c r="Q331" t="inlineStr"/>
       <c r="R331" t="inlineStr"/>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -17981,6 +19636,11 @@
       <c r="P332" t="inlineStr"/>
       <c r="Q332" t="inlineStr"/>
       <c r="R332" t="inlineStr"/>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -18033,6 +19693,11 @@
       <c r="P333" t="inlineStr"/>
       <c r="Q333" t="inlineStr"/>
       <c r="R333" t="inlineStr"/>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -18085,6 +19750,11 @@
       <c r="P334" t="inlineStr"/>
       <c r="Q334" t="inlineStr"/>
       <c r="R334" t="inlineStr"/>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -18137,6 +19807,11 @@
       <c r="P335" t="inlineStr"/>
       <c r="Q335" t="inlineStr"/>
       <c r="R335" t="inlineStr"/>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -18189,6 +19864,11 @@
       <c r="P336" t="inlineStr"/>
       <c r="Q336" t="inlineStr"/>
       <c r="R336" t="inlineStr"/>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -18241,6 +19921,11 @@
       <c r="P337" t="inlineStr"/>
       <c r="Q337" t="inlineStr"/>
       <c r="R337" t="inlineStr"/>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -18293,6 +19978,11 @@
       <c r="P338" t="inlineStr"/>
       <c r="Q338" t="inlineStr"/>
       <c r="R338" t="inlineStr"/>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -18345,6 +20035,11 @@
       <c r="P339" t="inlineStr"/>
       <c r="Q339" t="inlineStr"/>
       <c r="R339" t="inlineStr"/>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -18397,6 +20092,11 @@
       <c r="P340" t="inlineStr"/>
       <c r="Q340" t="inlineStr"/>
       <c r="R340" t="inlineStr"/>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -18449,6 +20149,11 @@
       <c r="P341" t="inlineStr"/>
       <c r="Q341" t="inlineStr"/>
       <c r="R341" t="inlineStr"/>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -18501,6 +20206,11 @@
       <c r="P342" t="inlineStr"/>
       <c r="Q342" t="inlineStr"/>
       <c r="R342" t="inlineStr"/>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -18553,6 +20263,11 @@
       <c r="P343" t="inlineStr"/>
       <c r="Q343" t="inlineStr"/>
       <c r="R343" t="inlineStr"/>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -18605,6 +20320,11 @@
       <c r="P344" t="inlineStr"/>
       <c r="Q344" t="inlineStr"/>
       <c r="R344" t="inlineStr"/>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -18657,6 +20377,11 @@
       <c r="P345" t="inlineStr"/>
       <c r="Q345" t="inlineStr"/>
       <c r="R345" t="inlineStr"/>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -18709,6 +20434,11 @@
       <c r="P346" t="inlineStr"/>
       <c r="Q346" t="inlineStr"/>
       <c r="R346" t="inlineStr"/>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -18761,6 +20491,11 @@
       <c r="P347" t="inlineStr"/>
       <c r="Q347" t="inlineStr"/>
       <c r="R347" t="inlineStr"/>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -18813,6 +20548,11 @@
       <c r="P348" t="inlineStr"/>
       <c r="Q348" t="inlineStr"/>
       <c r="R348" t="inlineStr"/>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -18865,6 +20605,11 @@
       <c r="P349" t="inlineStr"/>
       <c r="Q349" t="inlineStr"/>
       <c r="R349" t="inlineStr"/>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -18917,6 +20662,11 @@
       <c r="P350" t="inlineStr"/>
       <c r="Q350" t="inlineStr"/>
       <c r="R350" t="inlineStr"/>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -18969,6 +20719,11 @@
       <c r="P351" t="inlineStr"/>
       <c r="Q351" t="inlineStr"/>
       <c r="R351" t="inlineStr"/>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -19021,6 +20776,11 @@
       <c r="P352" t="inlineStr"/>
       <c r="Q352" t="inlineStr"/>
       <c r="R352" t="inlineStr"/>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -19073,6 +20833,11 @@
       <c r="P353" t="inlineStr"/>
       <c r="Q353" t="inlineStr"/>
       <c r="R353" t="inlineStr"/>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -19125,6 +20890,11 @@
       <c r="P354" t="inlineStr"/>
       <c r="Q354" t="inlineStr"/>
       <c r="R354" t="inlineStr"/>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -19177,6 +20947,11 @@
       <c r="P355" t="inlineStr"/>
       <c r="Q355" t="inlineStr"/>
       <c r="R355" t="inlineStr"/>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -19229,6 +21004,11 @@
       <c r="P356" t="inlineStr"/>
       <c r="Q356" t="inlineStr"/>
       <c r="R356" t="inlineStr"/>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -19281,6 +21061,11 @@
       <c r="P357" t="inlineStr"/>
       <c r="Q357" t="inlineStr"/>
       <c r="R357" t="inlineStr"/>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -19333,6 +21118,11 @@
       <c r="P358" t="inlineStr"/>
       <c r="Q358" t="inlineStr"/>
       <c r="R358" t="inlineStr"/>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -19385,6 +21175,11 @@
       <c r="P359" t="inlineStr"/>
       <c r="Q359" t="inlineStr"/>
       <c r="R359" t="inlineStr"/>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -19437,6 +21232,11 @@
       <c r="P360" t="inlineStr"/>
       <c r="Q360" t="inlineStr"/>
       <c r="R360" t="inlineStr"/>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -19489,6 +21289,11 @@
       <c r="P361" t="inlineStr"/>
       <c r="Q361" t="inlineStr"/>
       <c r="R361" t="inlineStr"/>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -19541,6 +21346,11 @@
       <c r="P362" t="inlineStr"/>
       <c r="Q362" t="inlineStr"/>
       <c r="R362" t="inlineStr"/>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -19593,6 +21403,11 @@
       <c r="P363" t="inlineStr"/>
       <c r="Q363" t="inlineStr"/>
       <c r="R363" t="inlineStr"/>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -19645,6 +21460,11 @@
       <c r="P364" t="inlineStr"/>
       <c r="Q364" t="inlineStr"/>
       <c r="R364" t="inlineStr"/>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -19697,6 +21517,11 @@
       <c r="P365" t="inlineStr"/>
       <c r="Q365" t="inlineStr"/>
       <c r="R365" t="inlineStr"/>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -19749,6 +21574,11 @@
       <c r="P366" t="inlineStr"/>
       <c r="Q366" t="inlineStr"/>
       <c r="R366" t="inlineStr"/>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -19801,6 +21631,11 @@
       <c r="P367" t="inlineStr"/>
       <c r="Q367" t="inlineStr"/>
       <c r="R367" t="inlineStr"/>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -19853,6 +21688,11 @@
       <c r="P368" t="inlineStr"/>
       <c r="Q368" t="inlineStr"/>
       <c r="R368" t="inlineStr"/>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -19905,6 +21745,11 @@
       <c r="P369" t="inlineStr"/>
       <c r="Q369" t="inlineStr"/>
       <c r="R369" t="inlineStr"/>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -19957,6 +21802,11 @@
       <c r="P370" t="inlineStr"/>
       <c r="Q370" t="inlineStr"/>
       <c r="R370" t="inlineStr"/>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -20009,6 +21859,11 @@
       <c r="P371" t="inlineStr"/>
       <c r="Q371" t="inlineStr"/>
       <c r="R371" t="inlineStr"/>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -20061,6 +21916,11 @@
       <c r="P372" t="inlineStr"/>
       <c r="Q372" t="inlineStr"/>
       <c r="R372" t="inlineStr"/>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -20113,6 +21973,11 @@
       <c r="P373" t="inlineStr"/>
       <c r="Q373" t="inlineStr"/>
       <c r="R373" t="inlineStr"/>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -20165,6 +22030,11 @@
       <c r="P374" t="inlineStr"/>
       <c r="Q374" t="inlineStr"/>
       <c r="R374" t="inlineStr"/>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -20217,6 +22087,11 @@
       <c r="P375" t="inlineStr"/>
       <c r="Q375" t="inlineStr"/>
       <c r="R375" t="inlineStr"/>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -20269,6 +22144,11 @@
       <c r="P376" t="inlineStr"/>
       <c r="Q376" t="inlineStr"/>
       <c r="R376" t="inlineStr"/>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -20321,6 +22201,11 @@
       <c r="P377" t="inlineStr"/>
       <c r="Q377" t="inlineStr"/>
       <c r="R377" t="inlineStr"/>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -20373,6 +22258,11 @@
       <c r="P378" t="inlineStr"/>
       <c r="Q378" t="inlineStr"/>
       <c r="R378" t="inlineStr"/>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -20425,6 +22315,11 @@
       <c r="P379" t="inlineStr"/>
       <c r="Q379" t="inlineStr"/>
       <c r="R379" t="inlineStr"/>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -20477,6 +22372,11 @@
       <c r="P380" t="inlineStr"/>
       <c r="Q380" t="inlineStr"/>
       <c r="R380" t="inlineStr"/>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -20529,6 +22429,11 @@
       <c r="P381" t="inlineStr"/>
       <c r="Q381" t="inlineStr"/>
       <c r="R381" t="inlineStr"/>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -20581,6 +22486,11 @@
       <c r="P382" t="inlineStr"/>
       <c r="Q382" t="inlineStr"/>
       <c r="R382" t="inlineStr"/>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -20633,6 +22543,11 @@
       <c r="P383" t="inlineStr"/>
       <c r="Q383" t="inlineStr"/>
       <c r="R383" t="inlineStr"/>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -20685,6 +22600,11 @@
       <c r="P384" t="inlineStr"/>
       <c r="Q384" t="inlineStr"/>
       <c r="R384" t="inlineStr"/>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -20737,6 +22657,11 @@
       <c r="P385" t="inlineStr"/>
       <c r="Q385" t="inlineStr"/>
       <c r="R385" t="inlineStr"/>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -20789,6 +22714,11 @@
       <c r="P386" t="inlineStr"/>
       <c r="Q386" t="inlineStr"/>
       <c r="R386" t="inlineStr"/>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -20841,6 +22771,11 @@
       <c r="P387" t="inlineStr"/>
       <c r="Q387" t="inlineStr"/>
       <c r="R387" t="inlineStr"/>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -20893,6 +22828,11 @@
       <c r="P388" t="inlineStr"/>
       <c r="Q388" t="inlineStr"/>
       <c r="R388" t="inlineStr"/>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -20945,6 +22885,11 @@
       <c r="P389" t="inlineStr"/>
       <c r="Q389" t="inlineStr"/>
       <c r="R389" t="inlineStr"/>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -20997,6 +22942,11 @@
       <c r="P390" t="inlineStr"/>
       <c r="Q390" t="inlineStr"/>
       <c r="R390" t="inlineStr"/>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -21049,6 +22999,11 @@
       <c r="P391" t="inlineStr"/>
       <c r="Q391" t="inlineStr"/>
       <c r="R391" t="inlineStr"/>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -21101,6 +23056,11 @@
       <c r="P392" t="inlineStr"/>
       <c r="Q392" t="inlineStr"/>
       <c r="R392" t="inlineStr"/>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -21153,6 +23113,11 @@
       <c r="P393" t="inlineStr"/>
       <c r="Q393" t="inlineStr"/>
       <c r="R393" t="inlineStr"/>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -21205,6 +23170,11 @@
       <c r="P394" t="inlineStr"/>
       <c r="Q394" t="inlineStr"/>
       <c r="R394" t="inlineStr"/>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -21257,6 +23227,11 @@
       <c r="P395" t="inlineStr"/>
       <c r="Q395" t="inlineStr"/>
       <c r="R395" t="inlineStr"/>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -21309,6 +23284,11 @@
       <c r="P396" t="inlineStr"/>
       <c r="Q396" t="inlineStr"/>
       <c r="R396" t="inlineStr"/>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -21361,6 +23341,11 @@
       <c r="P397" t="inlineStr"/>
       <c r="Q397" t="inlineStr"/>
       <c r="R397" t="inlineStr"/>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -21413,6 +23398,11 @@
       <c r="P398" t="inlineStr"/>
       <c r="Q398" t="inlineStr"/>
       <c r="R398" t="inlineStr"/>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -21465,6 +23455,11 @@
       <c r="P399" t="inlineStr"/>
       <c r="Q399" t="inlineStr"/>
       <c r="R399" t="inlineStr"/>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -21517,6 +23512,11 @@
       <c r="P400" t="inlineStr"/>
       <c r="Q400" t="inlineStr"/>
       <c r="R400" t="inlineStr"/>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -21569,6 +23569,11 @@
       <c r="P401" t="inlineStr"/>
       <c r="Q401" t="inlineStr"/>
       <c r="R401" t="inlineStr"/>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -21621,6 +23626,11 @@
       <c r="P402" t="inlineStr"/>
       <c r="Q402" t="inlineStr"/>
       <c r="R402" t="inlineStr"/>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -21673,6 +23683,11 @@
       <c r="P403" t="inlineStr"/>
       <c r="Q403" t="inlineStr"/>
       <c r="R403" t="inlineStr"/>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -21725,6 +23740,11 @@
       <c r="P404" t="inlineStr"/>
       <c r="Q404" t="inlineStr"/>
       <c r="R404" t="inlineStr"/>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -21777,6 +23797,11 @@
       <c r="P405" t="inlineStr"/>
       <c r="Q405" t="inlineStr"/>
       <c r="R405" t="inlineStr"/>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -21829,6 +23854,11 @@
       <c r="P406" t="inlineStr"/>
       <c r="Q406" t="inlineStr"/>
       <c r="R406" t="inlineStr"/>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -21881,6 +23911,11 @@
       <c r="P407" t="inlineStr"/>
       <c r="Q407" t="inlineStr"/>
       <c r="R407" t="inlineStr"/>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -21933,6 +23968,11 @@
       <c r="P408" t="inlineStr"/>
       <c r="Q408" t="inlineStr"/>
       <c r="R408" t="inlineStr"/>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -21985,6 +24025,11 @@
       <c r="P409" t="inlineStr"/>
       <c r="Q409" t="inlineStr"/>
       <c r="R409" t="inlineStr"/>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -22037,6 +24082,11 @@
       <c r="P410" t="inlineStr"/>
       <c r="Q410" t="inlineStr"/>
       <c r="R410" t="inlineStr"/>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -22089,6 +24139,11 @@
       <c r="P411" t="inlineStr"/>
       <c r="Q411" t="inlineStr"/>
       <c r="R411" t="inlineStr"/>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -22141,6 +24196,11 @@
       <c r="P412" t="inlineStr"/>
       <c r="Q412" t="inlineStr"/>
       <c r="R412" t="inlineStr"/>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -22193,6 +24253,11 @@
       <c r="P413" t="inlineStr"/>
       <c r="Q413" t="inlineStr"/>
       <c r="R413" t="inlineStr"/>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -22245,6 +24310,11 @@
       <c r="P414" t="inlineStr"/>
       <c r="Q414" t="inlineStr"/>
       <c r="R414" t="inlineStr"/>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -22297,6 +24367,11 @@
       <c r="P415" t="inlineStr"/>
       <c r="Q415" t="inlineStr"/>
       <c r="R415" t="inlineStr"/>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -22349,6 +24424,11 @@
       <c r="P416" t="inlineStr"/>
       <c r="Q416" t="inlineStr"/>
       <c r="R416" t="inlineStr"/>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -22401,6 +24481,11 @@
       <c r="P417" t="inlineStr"/>
       <c r="Q417" t="inlineStr"/>
       <c r="R417" t="inlineStr"/>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -22453,6 +24538,11 @@
       <c r="P418" t="inlineStr"/>
       <c r="Q418" t="inlineStr"/>
       <c r="R418" t="inlineStr"/>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -22505,6 +24595,11 @@
       <c r="P419" t="inlineStr"/>
       <c r="Q419" t="inlineStr"/>
       <c r="R419" t="inlineStr"/>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -22557,6 +24652,11 @@
       <c r="P420" t="inlineStr"/>
       <c r="Q420" t="inlineStr"/>
       <c r="R420" t="inlineStr"/>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -22609,6 +24709,11 @@
       <c r="P421" t="inlineStr"/>
       <c r="Q421" t="inlineStr"/>
       <c r="R421" t="inlineStr"/>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -22661,6 +24766,11 @@
       <c r="P422" t="inlineStr"/>
       <c r="Q422" t="inlineStr"/>
       <c r="R422" t="inlineStr"/>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -22713,6 +24823,11 @@
       <c r="P423" t="inlineStr"/>
       <c r="Q423" t="inlineStr"/>
       <c r="R423" t="inlineStr"/>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -22765,6 +24880,11 @@
       <c r="P424" t="inlineStr"/>
       <c r="Q424" t="inlineStr"/>
       <c r="R424" t="inlineStr"/>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -22817,6 +24937,11 @@
       <c r="P425" t="inlineStr"/>
       <c r="Q425" t="inlineStr"/>
       <c r="R425" t="inlineStr"/>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -22869,6 +24994,11 @@
       <c r="P426" t="inlineStr"/>
       <c r="Q426" t="inlineStr"/>
       <c r="R426" t="inlineStr"/>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -22921,6 +25051,11 @@
       <c r="P427" t="inlineStr"/>
       <c r="Q427" t="inlineStr"/>
       <c r="R427" t="inlineStr"/>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -22973,6 +25108,11 @@
       <c r="P428" t="inlineStr"/>
       <c r="Q428" t="inlineStr"/>
       <c r="R428" t="inlineStr"/>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -23025,6 +25165,11 @@
       <c r="P429" t="inlineStr"/>
       <c r="Q429" t="inlineStr"/>
       <c r="R429" t="inlineStr"/>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -23077,6 +25222,11 @@
       <c r="P430" t="inlineStr"/>
       <c r="Q430" t="inlineStr"/>
       <c r="R430" t="inlineStr"/>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -23129,6 +25279,11 @@
       <c r="P431" t="inlineStr"/>
       <c r="Q431" t="inlineStr"/>
       <c r="R431" t="inlineStr"/>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -23181,6 +25336,11 @@
       <c r="P432" t="inlineStr"/>
       <c r="Q432" t="inlineStr"/>
       <c r="R432" t="inlineStr"/>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -23233,6 +25393,11 @@
       <c r="P433" t="inlineStr"/>
       <c r="Q433" t="inlineStr"/>
       <c r="R433" t="inlineStr"/>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -23285,6 +25450,11 @@
       <c r="P434" t="inlineStr"/>
       <c r="Q434" t="inlineStr"/>
       <c r="R434" t="inlineStr"/>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -23337,6 +25507,11 @@
       <c r="P435" t="inlineStr"/>
       <c r="Q435" t="inlineStr"/>
       <c r="R435" t="inlineStr"/>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -23389,6 +25564,11 @@
       <c r="P436" t="inlineStr"/>
       <c r="Q436" t="inlineStr"/>
       <c r="R436" t="inlineStr"/>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -23441,6 +25621,11 @@
       <c r="P437" t="inlineStr"/>
       <c r="Q437" t="inlineStr"/>
       <c r="R437" t="inlineStr"/>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -23493,6 +25678,11 @@
       <c r="P438" t="inlineStr"/>
       <c r="Q438" t="inlineStr"/>
       <c r="R438" t="inlineStr"/>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -23545,6 +25735,11 @@
       <c r="P439" t="inlineStr"/>
       <c r="Q439" t="inlineStr"/>
       <c r="R439" t="inlineStr"/>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -23597,6 +25792,11 @@
       <c r="P440" t="inlineStr"/>
       <c r="Q440" t="inlineStr"/>
       <c r="R440" t="inlineStr"/>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -23649,6 +25849,11 @@
       <c r="P441" t="inlineStr"/>
       <c r="Q441" t="inlineStr"/>
       <c r="R441" t="inlineStr"/>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -23701,6 +25906,11 @@
       <c r="P442" t="inlineStr"/>
       <c r="Q442" t="inlineStr"/>
       <c r="R442" t="inlineStr"/>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -23753,6 +25963,11 @@
       <c r="P443" t="inlineStr"/>
       <c r="Q443" t="inlineStr"/>
       <c r="R443" t="inlineStr"/>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -23805,6 +26020,11 @@
       <c r="P444" t="inlineStr"/>
       <c r="Q444" t="inlineStr"/>
       <c r="R444" t="inlineStr"/>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -23857,6 +26077,11 @@
       <c r="P445" t="inlineStr"/>
       <c r="Q445" t="inlineStr"/>
       <c r="R445" t="inlineStr"/>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -23909,6 +26134,11 @@
       <c r="P446" t="inlineStr"/>
       <c r="Q446" t="inlineStr"/>
       <c r="R446" t="inlineStr"/>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -23961,6 +26191,11 @@
       <c r="P447" t="inlineStr"/>
       <c r="Q447" t="inlineStr"/>
       <c r="R447" t="inlineStr"/>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -24013,6 +26248,11 @@
       <c r="P448" t="inlineStr"/>
       <c r="Q448" t="inlineStr"/>
       <c r="R448" t="inlineStr"/>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -24065,6 +26305,11 @@
       <c r="P449" t="inlineStr"/>
       <c r="Q449" t="inlineStr"/>
       <c r="R449" t="inlineStr"/>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -24117,6 +26362,11 @@
       <c r="P450" t="inlineStr"/>
       <c r="Q450" t="inlineStr"/>
       <c r="R450" t="inlineStr"/>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -24169,6 +26419,11 @@
       <c r="P451" t="inlineStr"/>
       <c r="Q451" t="inlineStr"/>
       <c r="R451" t="inlineStr"/>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -24221,6 +26476,11 @@
       <c r="P452" t="inlineStr"/>
       <c r="Q452" t="inlineStr"/>
       <c r="R452" t="inlineStr"/>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -24273,6 +26533,11 @@
       <c r="P453" t="inlineStr"/>
       <c r="Q453" t="inlineStr"/>
       <c r="R453" t="inlineStr"/>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -24325,6 +26590,11 @@
       <c r="P454" t="inlineStr"/>
       <c r="Q454" t="inlineStr"/>
       <c r="R454" t="inlineStr"/>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -24377,6 +26647,11 @@
       <c r="P455" t="inlineStr"/>
       <c r="Q455" t="inlineStr"/>
       <c r="R455" t="inlineStr"/>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -24429,6 +26704,11 @@
       <c r="P456" t="inlineStr"/>
       <c r="Q456" t="inlineStr"/>
       <c r="R456" t="inlineStr"/>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -24481,6 +26761,11 @@
       <c r="P457" t="inlineStr"/>
       <c r="Q457" t="inlineStr"/>
       <c r="R457" t="inlineStr"/>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -24533,6 +26818,11 @@
       <c r="P458" t="inlineStr"/>
       <c r="Q458" t="inlineStr"/>
       <c r="R458" t="inlineStr"/>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -24585,6 +26875,11 @@
       <c r="P459" t="inlineStr"/>
       <c r="Q459" t="inlineStr"/>
       <c r="R459" t="inlineStr"/>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -24637,6 +26932,11 @@
       <c r="P460" t="inlineStr"/>
       <c r="Q460" t="inlineStr"/>
       <c r="R460" t="inlineStr"/>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -24689,6 +26989,11 @@
       <c r="P461" t="inlineStr"/>
       <c r="Q461" t="inlineStr"/>
       <c r="R461" t="inlineStr"/>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -24741,6 +27046,11 @@
       <c r="P462" t="inlineStr"/>
       <c r="Q462" t="inlineStr"/>
       <c r="R462" t="inlineStr"/>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -24793,6 +27103,11 @@
       <c r="P463" t="inlineStr"/>
       <c r="Q463" t="inlineStr"/>
       <c r="R463" t="inlineStr"/>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -24845,6 +27160,11 @@
       <c r="P464" t="inlineStr"/>
       <c r="Q464" t="inlineStr"/>
       <c r="R464" t="inlineStr"/>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -24897,6 +27217,11 @@
       <c r="P465" t="inlineStr"/>
       <c r="Q465" t="inlineStr"/>
       <c r="R465" t="inlineStr"/>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -24949,6 +27274,11 @@
       <c r="P466" t="inlineStr"/>
       <c r="Q466" t="inlineStr"/>
       <c r="R466" t="inlineStr"/>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -25001,6 +27331,11 @@
       <c r="P467" t="inlineStr"/>
       <c r="Q467" t="inlineStr"/>
       <c r="R467" t="inlineStr"/>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -25053,6 +27388,11 @@
       <c r="P468" t="inlineStr"/>
       <c r="Q468" t="inlineStr"/>
       <c r="R468" t="inlineStr"/>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -25105,6 +27445,11 @@
       <c r="P469" t="inlineStr"/>
       <c r="Q469" t="inlineStr"/>
       <c r="R469" t="inlineStr"/>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -25157,6 +27502,11 @@
       <c r="P470" t="inlineStr"/>
       <c r="Q470" t="inlineStr"/>
       <c r="R470" t="inlineStr"/>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -25209,6 +27559,11 @@
       <c r="P471" t="inlineStr"/>
       <c r="Q471" t="inlineStr"/>
       <c r="R471" t="inlineStr"/>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -25261,6 +27616,11 @@
       <c r="P472" t="inlineStr"/>
       <c r="Q472" t="inlineStr"/>
       <c r="R472" t="inlineStr"/>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -25313,6 +27673,11 @@
       <c r="P473" t="inlineStr"/>
       <c r="Q473" t="inlineStr"/>
       <c r="R473" t="inlineStr"/>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -25365,6 +27730,11 @@
       <c r="P474" t="inlineStr"/>
       <c r="Q474" t="inlineStr"/>
       <c r="R474" t="inlineStr"/>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -25417,6 +27787,11 @@
       <c r="P475" t="inlineStr"/>
       <c r="Q475" t="inlineStr"/>
       <c r="R475" t="inlineStr"/>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -25469,6 +27844,11 @@
       <c r="P476" t="inlineStr"/>
       <c r="Q476" t="inlineStr"/>
       <c r="R476" t="inlineStr"/>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -25521,6 +27901,11 @@
       <c r="P477" t="inlineStr"/>
       <c r="Q477" t="inlineStr"/>
       <c r="R477" t="inlineStr"/>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -25573,6 +27958,11 @@
       <c r="P478" t="inlineStr"/>
       <c r="Q478" t="inlineStr"/>
       <c r="R478" t="inlineStr"/>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -25625,6 +28015,11 @@
       <c r="P479" t="inlineStr"/>
       <c r="Q479" t="inlineStr"/>
       <c r="R479" t="inlineStr"/>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -25677,6 +28072,11 @@
       <c r="P480" t="inlineStr"/>
       <c r="Q480" t="inlineStr"/>
       <c r="R480" t="inlineStr"/>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -25729,6 +28129,11 @@
       <c r="P481" t="inlineStr"/>
       <c r="Q481" t="inlineStr"/>
       <c r="R481" t="inlineStr"/>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -25781,6 +28186,11 @@
       <c r="P482" t="inlineStr"/>
       <c r="Q482" t="inlineStr"/>
       <c r="R482" t="inlineStr"/>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -25833,6 +28243,11 @@
       <c r="P483" t="inlineStr"/>
       <c r="Q483" t="inlineStr"/>
       <c r="R483" t="inlineStr"/>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -25885,6 +28300,11 @@
       <c r="P484" t="inlineStr"/>
       <c r="Q484" t="inlineStr"/>
       <c r="R484" t="inlineStr"/>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -25937,6 +28357,11 @@
       <c r="P485" t="inlineStr"/>
       <c r="Q485" t="inlineStr"/>
       <c r="R485" t="inlineStr"/>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -25989,6 +28414,11 @@
       <c r="P486" t="inlineStr"/>
       <c r="Q486" t="inlineStr"/>
       <c r="R486" t="inlineStr"/>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -26041,6 +28471,11 @@
       <c r="P487" t="inlineStr"/>
       <c r="Q487" t="inlineStr"/>
       <c r="R487" t="inlineStr"/>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -26093,6 +28528,11 @@
       <c r="P488" t="inlineStr"/>
       <c r="Q488" t="inlineStr"/>
       <c r="R488" t="inlineStr"/>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -26145,6 +28585,11 @@
       <c r="P489" t="inlineStr"/>
       <c r="Q489" t="inlineStr"/>
       <c r="R489" t="inlineStr"/>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -26197,6 +28642,11 @@
       <c r="P490" t="inlineStr"/>
       <c r="Q490" t="inlineStr"/>
       <c r="R490" t="inlineStr"/>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -26249,6 +28699,11 @@
       <c r="P491" t="inlineStr"/>
       <c r="Q491" t="inlineStr"/>
       <c r="R491" t="inlineStr"/>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -26301,6 +28756,11 @@
       <c r="P492" t="inlineStr"/>
       <c r="Q492" t="inlineStr"/>
       <c r="R492" t="inlineStr"/>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -26353,6 +28813,11 @@
       <c r="P493" t="inlineStr"/>
       <c r="Q493" t="inlineStr"/>
       <c r="R493" t="inlineStr"/>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -26405,6 +28870,11 @@
       <c r="P494" t="inlineStr"/>
       <c r="Q494" t="inlineStr"/>
       <c r="R494" t="inlineStr"/>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -26457,6 +28927,11 @@
       <c r="P495" t="inlineStr"/>
       <c r="Q495" t="inlineStr"/>
       <c r="R495" t="inlineStr"/>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -26509,6 +28984,11 @@
       <c r="P496" t="inlineStr"/>
       <c r="Q496" t="inlineStr"/>
       <c r="R496" t="inlineStr"/>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -26561,6 +29041,11 @@
       <c r="P497" t="inlineStr"/>
       <c r="Q497" t="inlineStr"/>
       <c r="R497" t="inlineStr"/>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -26613,6 +29098,11 @@
       <c r="P498" t="inlineStr"/>
       <c r="Q498" t="inlineStr"/>
       <c r="R498" t="inlineStr"/>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -26665,6 +29155,11 @@
       <c r="P499" t="inlineStr"/>
       <c r="Q499" t="inlineStr"/>
       <c r="R499" t="inlineStr"/>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -26717,6 +29212,11 @@
       <c r="P500" t="inlineStr"/>
       <c r="Q500" t="inlineStr"/>
       <c r="R500" t="inlineStr"/>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -26769,6 +29269,11 @@
       <c r="P501" t="inlineStr"/>
       <c r="Q501" t="inlineStr"/>
       <c r="R501" t="inlineStr"/>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -26821,6 +29326,11 @@
       <c r="P502" t="inlineStr"/>
       <c r="Q502" t="inlineStr"/>
       <c r="R502" t="inlineStr"/>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -26873,6 +29383,11 @@
       <c r="P503" t="inlineStr"/>
       <c r="Q503" t="inlineStr"/>
       <c r="R503" t="inlineStr"/>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -26925,6 +29440,11 @@
       <c r="P504" t="inlineStr"/>
       <c r="Q504" t="inlineStr"/>
       <c r="R504" t="inlineStr"/>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -26977,6 +29497,11 @@
       <c r="P505" t="inlineStr"/>
       <c r="Q505" t="inlineStr"/>
       <c r="R505" t="inlineStr"/>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -27029,6 +29554,11 @@
       <c r="P506" t="inlineStr"/>
       <c r="Q506" t="inlineStr"/>
       <c r="R506" t="inlineStr"/>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -27081,6 +29611,11 @@
       <c r="P507" t="inlineStr"/>
       <c r="Q507" t="inlineStr"/>
       <c r="R507" t="inlineStr"/>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -27133,6 +29668,11 @@
       <c r="P508" t="inlineStr"/>
       <c r="Q508" t="inlineStr"/>
       <c r="R508" t="inlineStr"/>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -27185,6 +29725,11 @@
       <c r="P509" t="inlineStr"/>
       <c r="Q509" t="inlineStr"/>
       <c r="R509" t="inlineStr"/>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -27237,6 +29782,11 @@
       <c r="P510" t="inlineStr"/>
       <c r="Q510" t="inlineStr"/>
       <c r="R510" t="inlineStr"/>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -27289,6 +29839,11 @@
       <c r="P511" t="inlineStr"/>
       <c r="Q511" t="inlineStr"/>
       <c r="R511" t="inlineStr"/>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -27341,6 +29896,11 @@
       <c r="P512" t="inlineStr"/>
       <c r="Q512" t="inlineStr"/>
       <c r="R512" t="inlineStr"/>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -27393,6 +29953,11 @@
       <c r="P513" t="inlineStr"/>
       <c r="Q513" t="inlineStr"/>
       <c r="R513" t="inlineStr"/>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -27445,6 +30010,11 @@
       <c r="P514" t="inlineStr"/>
       <c r="Q514" t="inlineStr"/>
       <c r="R514" t="inlineStr"/>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -27497,6 +30067,11 @@
       <c r="P515" t="inlineStr"/>
       <c r="Q515" t="inlineStr"/>
       <c r="R515" t="inlineStr"/>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -27549,6 +30124,11 @@
       <c r="P516" t="inlineStr"/>
       <c r="Q516" t="inlineStr"/>
       <c r="R516" t="inlineStr"/>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -27601,6 +30181,11 @@
       <c r="P517" t="inlineStr"/>
       <c r="Q517" t="inlineStr"/>
       <c r="R517" t="inlineStr"/>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -27653,6 +30238,11 @@
       <c r="P518" t="inlineStr"/>
       <c r="Q518" t="inlineStr"/>
       <c r="R518" t="inlineStr"/>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -27705,6 +30295,11 @@
       <c r="P519" t="inlineStr"/>
       <c r="Q519" t="inlineStr"/>
       <c r="R519" t="inlineStr"/>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -27757,6 +30352,11 @@
       <c r="P520" t="inlineStr"/>
       <c r="Q520" t="inlineStr"/>
       <c r="R520" t="inlineStr"/>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -27809,6 +30409,11 @@
       <c r="P521" t="inlineStr"/>
       <c r="Q521" t="inlineStr"/>
       <c r="R521" t="inlineStr"/>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -27861,6 +30466,11 @@
       <c r="P522" t="inlineStr"/>
       <c r="Q522" t="inlineStr"/>
       <c r="R522" t="inlineStr"/>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -27913,6 +30523,11 @@
       <c r="P523" t="inlineStr"/>
       <c r="Q523" t="inlineStr"/>
       <c r="R523" t="inlineStr"/>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -27965,6 +30580,11 @@
       <c r="P524" t="inlineStr"/>
       <c r="Q524" t="inlineStr"/>
       <c r="R524" t="inlineStr"/>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -28017,6 +30637,11 @@
       <c r="P525" t="inlineStr"/>
       <c r="Q525" t="inlineStr"/>
       <c r="R525" t="inlineStr"/>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -28069,6 +30694,11 @@
       <c r="P526" t="inlineStr"/>
       <c r="Q526" t="inlineStr"/>
       <c r="R526" t="inlineStr"/>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -28121,6 +30751,11 @@
       <c r="P527" t="inlineStr"/>
       <c r="Q527" t="inlineStr"/>
       <c r="R527" t="inlineStr"/>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -28173,6 +30808,11 @@
       <c r="P528" t="inlineStr"/>
       <c r="Q528" t="inlineStr"/>
       <c r="R528" t="inlineStr"/>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -28225,6 +30865,11 @@
       <c r="P529" t="inlineStr"/>
       <c r="Q529" t="inlineStr"/>
       <c r="R529" t="inlineStr"/>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -28277,6 +30922,11 @@
       <c r="P530" t="inlineStr"/>
       <c r="Q530" t="inlineStr"/>
       <c r="R530" t="inlineStr"/>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -28329,6 +30979,11 @@
       <c r="P531" t="inlineStr"/>
       <c r="Q531" t="inlineStr"/>
       <c r="R531" t="inlineStr"/>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -28381,6 +31036,11 @@
       <c r="P532" t="inlineStr"/>
       <c r="Q532" t="inlineStr"/>
       <c r="R532" t="inlineStr"/>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -28433,6 +31093,11 @@
       <c r="P533" t="inlineStr"/>
       <c r="Q533" t="inlineStr"/>
       <c r="R533" t="inlineStr"/>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -28485,6 +31150,11 @@
       <c r="P534" t="inlineStr"/>
       <c r="Q534" t="inlineStr"/>
       <c r="R534" t="inlineStr"/>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -28537,6 +31207,11 @@
       <c r="P535" t="inlineStr"/>
       <c r="Q535" t="inlineStr"/>
       <c r="R535" t="inlineStr"/>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -28589,6 +31264,11 @@
       <c r="P536" t="inlineStr"/>
       <c r="Q536" t="inlineStr"/>
       <c r="R536" t="inlineStr"/>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -28641,6 +31321,11 @@
       <c r="P537" t="inlineStr"/>
       <c r="Q537" t="inlineStr"/>
       <c r="R537" t="inlineStr"/>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -28693,6 +31378,11 @@
       <c r="P538" t="inlineStr"/>
       <c r="Q538" t="inlineStr"/>
       <c r="R538" t="inlineStr"/>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -28745,6 +31435,11 @@
       <c r="P539" t="inlineStr"/>
       <c r="Q539" t="inlineStr"/>
       <c r="R539" t="inlineStr"/>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -28797,6 +31492,11 @@
       <c r="P540" t="inlineStr"/>
       <c r="Q540" t="inlineStr"/>
       <c r="R540" t="inlineStr"/>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -28849,6 +31549,11 @@
       <c r="P541" t="inlineStr"/>
       <c r="Q541" t="inlineStr"/>
       <c r="R541" t="inlineStr"/>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -28901,6 +31606,11 @@
       <c r="P542" t="inlineStr"/>
       <c r="Q542" t="inlineStr"/>
       <c r="R542" t="inlineStr"/>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -28953,6 +31663,11 @@
       <c r="P543" t="inlineStr"/>
       <c r="Q543" t="inlineStr"/>
       <c r="R543" t="inlineStr"/>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -29005,6 +31720,11 @@
       <c r="P544" t="inlineStr"/>
       <c r="Q544" t="inlineStr"/>
       <c r="R544" t="inlineStr"/>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -29057,6 +31777,11 @@
       <c r="P545" t="inlineStr"/>
       <c r="Q545" t="inlineStr"/>
       <c r="R545" t="inlineStr"/>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -29109,6 +31834,11 @@
       <c r="P546" t="inlineStr"/>
       <c r="Q546" t="inlineStr"/>
       <c r="R546" t="inlineStr"/>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -29161,6 +31891,11 @@
       <c r="P547" t="inlineStr"/>
       <c r="Q547" t="inlineStr"/>
       <c r="R547" t="inlineStr"/>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -29213,6 +31948,11 @@
       <c r="P548" t="inlineStr"/>
       <c r="Q548" t="inlineStr"/>
       <c r="R548" t="inlineStr"/>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -29265,6 +32005,11 @@
       <c r="P549" t="inlineStr"/>
       <c r="Q549" t="inlineStr"/>
       <c r="R549" t="inlineStr"/>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -29317,6 +32062,11 @@
       <c r="P550" t="inlineStr"/>
       <c r="Q550" t="inlineStr"/>
       <c r="R550" t="inlineStr"/>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -29369,6 +32119,11 @@
       <c r="P551" t="inlineStr"/>
       <c r="Q551" t="inlineStr"/>
       <c r="R551" t="inlineStr"/>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -29421,6 +32176,11 @@
       <c r="P552" t="inlineStr"/>
       <c r="Q552" t="inlineStr"/>
       <c r="R552" t="inlineStr"/>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -29473,6 +32233,11 @@
       <c r="P553" t="inlineStr"/>
       <c r="Q553" t="inlineStr"/>
       <c r="R553" t="inlineStr"/>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -29525,6 +32290,11 @@
       <c r="P554" t="inlineStr"/>
       <c r="Q554" t="inlineStr"/>
       <c r="R554" t="inlineStr"/>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -29577,6 +32347,11 @@
       <c r="P555" t="inlineStr"/>
       <c r="Q555" t="inlineStr"/>
       <c r="R555" t="inlineStr"/>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -29629,6 +32404,11 @@
       <c r="P556" t="inlineStr"/>
       <c r="Q556" t="inlineStr"/>
       <c r="R556" t="inlineStr"/>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -29681,6 +32461,11 @@
       <c r="P557" t="inlineStr"/>
       <c r="Q557" t="inlineStr"/>
       <c r="R557" t="inlineStr"/>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -29733,6 +32518,11 @@
       <c r="P558" t="inlineStr"/>
       <c r="Q558" t="inlineStr"/>
       <c r="R558" t="inlineStr"/>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -29785,6 +32575,11 @@
       <c r="P559" t="inlineStr"/>
       <c r="Q559" t="inlineStr"/>
       <c r="R559" t="inlineStr"/>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -29837,6 +32632,11 @@
       <c r="P560" t="inlineStr"/>
       <c r="Q560" t="inlineStr"/>
       <c r="R560" t="inlineStr"/>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -29889,6 +32689,11 @@
       <c r="P561" t="inlineStr"/>
       <c r="Q561" t="inlineStr"/>
       <c r="R561" t="inlineStr"/>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -29941,6 +32746,11 @@
       <c r="P562" t="inlineStr"/>
       <c r="Q562" t="inlineStr"/>
       <c r="R562" t="inlineStr"/>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -29993,6 +32803,11 @@
       <c r="P563" t="inlineStr"/>
       <c r="Q563" t="inlineStr"/>
       <c r="R563" t="inlineStr"/>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -30045,6 +32860,11 @@
       <c r="P564" t="inlineStr"/>
       <c r="Q564" t="inlineStr"/>
       <c r="R564" t="inlineStr"/>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -30097,6 +32917,11 @@
       <c r="P565" t="inlineStr"/>
       <c r="Q565" t="inlineStr"/>
       <c r="R565" t="inlineStr"/>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -30149,6 +32974,11 @@
       <c r="P566" t="inlineStr"/>
       <c r="Q566" t="inlineStr"/>
       <c r="R566" t="inlineStr"/>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -30201,6 +33031,11 @@
       <c r="P567" t="inlineStr"/>
       <c r="Q567" t="inlineStr"/>
       <c r="R567" t="inlineStr"/>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -30253,6 +33088,11 @@
       <c r="P568" t="inlineStr"/>
       <c r="Q568" t="inlineStr"/>
       <c r="R568" t="inlineStr"/>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -30305,6 +33145,11 @@
       <c r="P569" t="inlineStr"/>
       <c r="Q569" t="inlineStr"/>
       <c r="R569" t="inlineStr"/>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -30357,6 +33202,11 @@
       <c r="P570" t="inlineStr"/>
       <c r="Q570" t="inlineStr"/>
       <c r="R570" t="inlineStr"/>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -30409,6 +33259,11 @@
       <c r="P571" t="inlineStr"/>
       <c r="Q571" t="inlineStr"/>
       <c r="R571" t="inlineStr"/>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -30461,6 +33316,11 @@
       <c r="P572" t="inlineStr"/>
       <c r="Q572" t="inlineStr"/>
       <c r="R572" t="inlineStr"/>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -30513,6 +33373,11 @@
       <c r="P573" t="inlineStr"/>
       <c r="Q573" t="inlineStr"/>
       <c r="R573" t="inlineStr"/>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -30565,6 +33430,11 @@
       <c r="P574" t="inlineStr"/>
       <c r="Q574" t="inlineStr"/>
       <c r="R574" t="inlineStr"/>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -30617,6 +33487,11 @@
       <c r="P575" t="inlineStr"/>
       <c r="Q575" t="inlineStr"/>
       <c r="R575" t="inlineStr"/>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -30669,6 +33544,11 @@
       <c r="P576" t="inlineStr"/>
       <c r="Q576" t="inlineStr"/>
       <c r="R576" t="inlineStr"/>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -30721,6 +33601,11 @@
       <c r="P577" t="inlineStr"/>
       <c r="Q577" t="inlineStr"/>
       <c r="R577" t="inlineStr"/>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -30773,6 +33658,11 @@
       <c r="P578" t="inlineStr"/>
       <c r="Q578" t="inlineStr"/>
       <c r="R578" t="inlineStr"/>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -30825,6 +33715,11 @@
       <c r="P579" t="inlineStr"/>
       <c r="Q579" t="inlineStr"/>
       <c r="R579" t="inlineStr"/>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -30877,6 +33772,11 @@
       <c r="P580" t="inlineStr"/>
       <c r="Q580" t="inlineStr"/>
       <c r="R580" t="inlineStr"/>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -30929,6 +33829,11 @@
       <c r="P581" t="inlineStr"/>
       <c r="Q581" t="inlineStr"/>
       <c r="R581" t="inlineStr"/>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -30979,6 +33884,11 @@
       <c r="P582" t="inlineStr"/>
       <c r="Q582" t="inlineStr"/>
       <c r="R582" t="inlineStr"/>
+      <c r="S582" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -31029,6 +33939,11 @@
       <c r="P583" t="inlineStr"/>
       <c r="Q583" t="inlineStr"/>
       <c r="R583" t="inlineStr"/>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -31079,6 +33994,11 @@
       <c r="P584" t="inlineStr"/>
       <c r="Q584" t="inlineStr"/>
       <c r="R584" t="inlineStr"/>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -31129,6 +34049,11 @@
       <c r="P585" t="inlineStr"/>
       <c r="Q585" t="inlineStr"/>
       <c r="R585" t="inlineStr"/>
+      <c r="S585" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -31179,6 +34104,11 @@
       <c r="P586" t="inlineStr"/>
       <c r="Q586" t="inlineStr"/>
       <c r="R586" t="inlineStr"/>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -31229,6 +34159,11 @@
       <c r="P587" t="inlineStr"/>
       <c r="Q587" t="inlineStr"/>
       <c r="R587" t="inlineStr"/>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -31279,6 +34214,11 @@
       <c r="P588" t="inlineStr"/>
       <c r="Q588" t="inlineStr"/>
       <c r="R588" t="inlineStr"/>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -31329,6 +34269,11 @@
       <c r="P589" t="inlineStr"/>
       <c r="Q589" t="inlineStr"/>
       <c r="R589" t="inlineStr"/>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -31379,6 +34324,11 @@
       <c r="P590" t="inlineStr"/>
       <c r="Q590" t="inlineStr"/>
       <c r="R590" t="inlineStr"/>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -31429,6 +34379,11 @@
       <c r="P591" t="inlineStr"/>
       <c r="Q591" t="inlineStr"/>
       <c r="R591" t="inlineStr"/>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -31479,6 +34434,11 @@
       <c r="P592" t="inlineStr"/>
       <c r="Q592" t="inlineStr"/>
       <c r="R592" t="inlineStr"/>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -31529,6 +34489,11 @@
       <c r="P593" t="inlineStr"/>
       <c r="Q593" t="inlineStr"/>
       <c r="R593" t="inlineStr"/>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -31579,6 +34544,11 @@
       <c r="P594" t="inlineStr"/>
       <c r="Q594" t="inlineStr"/>
       <c r="R594" t="inlineStr"/>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -31629,6 +34599,11 @@
       <c r="P595" t="inlineStr"/>
       <c r="Q595" t="inlineStr"/>
       <c r="R595" t="inlineStr"/>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -31679,6 +34654,11 @@
       <c r="P596" t="inlineStr"/>
       <c r="Q596" t="inlineStr"/>
       <c r="R596" t="inlineStr"/>
+      <c r="S596" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -31729,6 +34709,11 @@
       <c r="P597" t="inlineStr"/>
       <c r="Q597" t="inlineStr"/>
       <c r="R597" t="inlineStr"/>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -31779,6 +34764,11 @@
       <c r="P598" t="inlineStr"/>
       <c r="Q598" t="inlineStr"/>
       <c r="R598" t="inlineStr"/>
+      <c r="S598" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -31829,6 +34819,11 @@
       <c r="P599" t="inlineStr"/>
       <c r="Q599" t="inlineStr"/>
       <c r="R599" t="inlineStr"/>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -31879,6 +34874,11 @@
       <c r="P600" t="inlineStr"/>
       <c r="Q600" t="inlineStr"/>
       <c r="R600" t="inlineStr"/>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -31929,6 +34929,11 @@
       <c r="P601" t="inlineStr"/>
       <c r="Q601" t="inlineStr"/>
       <c r="R601" t="inlineStr"/>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -31979,6 +34984,11 @@
       <c r="P602" t="inlineStr"/>
       <c r="Q602" t="inlineStr"/>
       <c r="R602" t="inlineStr"/>
+      <c r="S602" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -32029,6 +35039,11 @@
       <c r="P603" t="inlineStr"/>
       <c r="Q603" t="inlineStr"/>
       <c r="R603" t="inlineStr"/>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -32079,6 +35094,11 @@
       <c r="P604" t="inlineStr"/>
       <c r="Q604" t="inlineStr"/>
       <c r="R604" t="inlineStr"/>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -32129,6 +35149,11 @@
       <c r="P605" t="inlineStr"/>
       <c r="Q605" t="inlineStr"/>
       <c r="R605" t="inlineStr"/>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -32179,6 +35204,11 @@
       <c r="P606" t="inlineStr"/>
       <c r="Q606" t="inlineStr"/>
       <c r="R606" t="inlineStr"/>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -32225,6 +35255,11 @@
       <c r="P607" t="inlineStr"/>
       <c r="Q607" t="inlineStr"/>
       <c r="R607" t="inlineStr"/>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -32275,6 +35310,11 @@
       <c r="P608" t="inlineStr"/>
       <c r="Q608" t="inlineStr"/>
       <c r="R608" t="inlineStr"/>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -32325,6 +35365,11 @@
       <c r="P609" t="inlineStr"/>
       <c r="Q609" t="inlineStr"/>
       <c r="R609" t="inlineStr"/>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -32375,6 +35420,11 @@
       <c r="P610" t="inlineStr"/>
       <c r="Q610" t="inlineStr"/>
       <c r="R610" t="inlineStr"/>
+      <c r="S610" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -32425,6 +35475,11 @@
       <c r="P611" t="inlineStr"/>
       <c r="Q611" t="inlineStr"/>
       <c r="R611" t="inlineStr"/>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -32475,6 +35530,11 @@
       <c r="P612" t="inlineStr"/>
       <c r="Q612" t="inlineStr"/>
       <c r="R612" t="inlineStr"/>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -32525,6 +35585,11 @@
       <c r="P613" t="inlineStr"/>
       <c r="Q613" t="inlineStr"/>
       <c r="R613" t="inlineStr"/>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -32575,6 +35640,11 @@
       <c r="P614" t="inlineStr"/>
       <c r="Q614" t="inlineStr"/>
       <c r="R614" t="inlineStr"/>
+      <c r="S614" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -32625,6 +35695,11 @@
       <c r="P615" t="inlineStr"/>
       <c r="Q615" t="inlineStr"/>
       <c r="R615" t="inlineStr"/>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -32675,6 +35750,11 @@
       <c r="P616" t="inlineStr"/>
       <c r="Q616" t="inlineStr"/>
       <c r="R616" t="inlineStr"/>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -32725,6 +35805,11 @@
       <c r="P617" t="inlineStr"/>
       <c r="Q617" t="inlineStr"/>
       <c r="R617" t="inlineStr"/>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -32775,6 +35860,11 @@
       <c r="P618" t="inlineStr"/>
       <c r="Q618" t="inlineStr"/>
       <c r="R618" t="inlineStr"/>
+      <c r="S618" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -32825,6 +35915,11 @@
       <c r="P619" t="inlineStr"/>
       <c r="Q619" t="inlineStr"/>
       <c r="R619" t="inlineStr"/>
+      <c r="S619" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -32875,6 +35970,11 @@
       <c r="P620" t="inlineStr"/>
       <c r="Q620" t="inlineStr"/>
       <c r="R620" t="inlineStr"/>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -32925,6 +36025,11 @@
       <c r="P621" t="inlineStr"/>
       <c r="Q621" t="inlineStr"/>
       <c r="R621" t="inlineStr"/>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -32975,6 +36080,11 @@
       <c r="P622" t="inlineStr"/>
       <c r="Q622" t="inlineStr"/>
       <c r="R622" t="inlineStr"/>
+      <c r="S622" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -33025,6 +36135,11 @@
       <c r="P623" t="inlineStr"/>
       <c r="Q623" t="inlineStr"/>
       <c r="R623" t="inlineStr"/>
+      <c r="S623" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -33075,6 +36190,11 @@
       <c r="P624" t="inlineStr"/>
       <c r="Q624" t="inlineStr"/>
       <c r="R624" t="inlineStr"/>
+      <c r="S624" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -33125,6 +36245,11 @@
       <c r="P625" t="inlineStr"/>
       <c r="Q625" t="inlineStr"/>
       <c r="R625" t="inlineStr"/>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -33175,6 +36300,11 @@
       <c r="P626" t="inlineStr"/>
       <c r="Q626" t="inlineStr"/>
       <c r="R626" t="inlineStr"/>
+      <c r="S626" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -33225,6 +36355,11 @@
       <c r="P627" t="inlineStr"/>
       <c r="Q627" t="inlineStr"/>
       <c r="R627" t="inlineStr"/>
+      <c r="S627" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -33275,6 +36410,11 @@
       <c r="P628" t="inlineStr"/>
       <c r="Q628" t="inlineStr"/>
       <c r="R628" t="inlineStr"/>
+      <c r="S628" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -33325,6 +36465,11 @@
       <c r="P629" t="inlineStr"/>
       <c r="Q629" t="inlineStr"/>
       <c r="R629" t="inlineStr"/>
+      <c r="S629" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -33375,6 +36520,11 @@
       <c r="P630" t="inlineStr"/>
       <c r="Q630" t="inlineStr"/>
       <c r="R630" t="inlineStr"/>
+      <c r="S630" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -33425,6 +36575,11 @@
       <c r="P631" t="inlineStr"/>
       <c r="Q631" t="inlineStr"/>
       <c r="R631" t="inlineStr"/>
+      <c r="S631" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -33475,6 +36630,11 @@
       <c r="P632" t="inlineStr"/>
       <c r="Q632" t="inlineStr"/>
       <c r="R632" t="inlineStr"/>
+      <c r="S632" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -33525,6 +36685,11 @@
       <c r="P633" t="inlineStr"/>
       <c r="Q633" t="inlineStr"/>
       <c r="R633" t="inlineStr"/>
+      <c r="S633" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -33575,6 +36740,11 @@
       <c r="P634" t="inlineStr"/>
       <c r="Q634" t="inlineStr"/>
       <c r="R634" t="inlineStr"/>
+      <c r="S634" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -33625,6 +36795,11 @@
       <c r="P635" t="inlineStr"/>
       <c r="Q635" t="inlineStr"/>
       <c r="R635" t="inlineStr"/>
+      <c r="S635" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -33675,6 +36850,11 @@
       <c r="P636" t="inlineStr"/>
       <c r="Q636" t="inlineStr"/>
       <c r="R636" t="inlineStr"/>
+      <c r="S636" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -33725,6 +36905,11 @@
       <c r="P637" t="inlineStr"/>
       <c r="Q637" t="inlineStr"/>
       <c r="R637" t="inlineStr"/>
+      <c r="S637" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -33775,6 +36960,11 @@
       <c r="P638" t="inlineStr"/>
       <c r="Q638" t="inlineStr"/>
       <c r="R638" t="inlineStr"/>
+      <c r="S638" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -33825,6 +37015,11 @@
       <c r="P639" t="inlineStr"/>
       <c r="Q639" t="inlineStr"/>
       <c r="R639" t="inlineStr"/>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -33875,6 +37070,11 @@
       <c r="P640" t="inlineStr"/>
       <c r="Q640" t="inlineStr"/>
       <c r="R640" t="inlineStr"/>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -33925,6 +37125,11 @@
       <c r="P641" t="inlineStr"/>
       <c r="Q641" t="inlineStr"/>
       <c r="R641" t="inlineStr"/>
+      <c r="S641" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -33975,6 +37180,11 @@
       <c r="P642" t="inlineStr"/>
       <c r="Q642" t="inlineStr"/>
       <c r="R642" t="inlineStr"/>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -34025,6 +37235,11 @@
       <c r="P643" t="inlineStr"/>
       <c r="Q643" t="inlineStr"/>
       <c r="R643" t="inlineStr"/>
+      <c r="S643" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -34075,6 +37290,11 @@
       <c r="P644" t="inlineStr"/>
       <c r="Q644" t="inlineStr"/>
       <c r="R644" t="inlineStr"/>
+      <c r="S644" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -34125,6 +37345,11 @@
       <c r="P645" t="inlineStr"/>
       <c r="Q645" t="inlineStr"/>
       <c r="R645" t="inlineStr"/>
+      <c r="S645" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -34175,6 +37400,11 @@
       <c r="P646" t="inlineStr"/>
       <c r="Q646" t="inlineStr"/>
       <c r="R646" t="inlineStr"/>
+      <c r="S646" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -34225,6 +37455,11 @@
       <c r="P647" t="inlineStr"/>
       <c r="Q647" t="inlineStr"/>
       <c r="R647" t="inlineStr"/>
+      <c r="S647" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -34275,6 +37510,11 @@
       <c r="P648" t="inlineStr"/>
       <c r="Q648" t="inlineStr"/>
       <c r="R648" t="inlineStr"/>
+      <c r="S648" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -34325,6 +37565,11 @@
       <c r="P649" t="inlineStr"/>
       <c r="Q649" t="inlineStr"/>
       <c r="R649" t="inlineStr"/>
+      <c r="S649" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -34375,6 +37620,11 @@
       <c r="P650" t="inlineStr"/>
       <c r="Q650" t="inlineStr"/>
       <c r="R650" t="inlineStr"/>
+      <c r="S650" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -34425,6 +37675,11 @@
       <c r="P651" t="inlineStr"/>
       <c r="Q651" t="inlineStr"/>
       <c r="R651" t="inlineStr"/>
+      <c r="S651" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -34475,6 +37730,11 @@
       <c r="P652" t="inlineStr"/>
       <c r="Q652" t="inlineStr"/>
       <c r="R652" t="inlineStr"/>
+      <c r="S652" t="inlineStr">
+        <is>
+          <t>Unidades Zonales (UZ)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_uz_asesoramiento.xlsx
+++ b/output/bases_limpias/Grupo_05_ASISTENCIAS_SIMILAR/df_uz_asesoramiento.xlsx
@@ -419,52 +419,52 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Nivel de Gobierno (Gobierno Nacional/Gobierno Regional/ Gobierno Local)</t>
+          <t>nivel_de_gobierno_gobierno_nacional_gobierno_regional_gobier</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Tipo de entidad (GR,MP,MD,DRE/GRE,UGEL, opcional Director de la I.E.)</t>
+          <t>tipo_de_entidad_gr_mp_md_dre_gre_ugel_opcional_director_de_l</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Nombre de entidad (en el caso de que sea un director de la I.E., colocar el código local de la I.E)</t>
+          <t>nombre_de_entidad_en_el_caso_de_que_sea_un_director_de_la_i</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Nombre de la Unidad Zonal</t>
+          <t>nombre_de_la_unidad_zonal</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Número de participantes</t>
+          <t>numero_de_participantes</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tema (1. Fortalecimiento de capacidades en gestionar inversiones. 2. Fortalecimiento de capacidades en gestionar otras intervenciones. 3. Fortalecimiento de capacidades en herramientas de gestión de la infraestructura educativa. 4. Fortalecimiento de capacidades en el marco normativo de la infraestructura educativa. 5. Fortalecimiento de capacidades en el recojo de información, diagnósticos, priorización o modalidades de financiamiento.</t>
+          <t>tema_1_fortalecimiento_de_capacidades_en_gestionar_inversion</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Título del asesoramiento o asistencia tècnica</t>
+          <t>titulo_del_asesoramiento_o_asistencia_tecnica</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
